--- a/multiSchoolOutput/01_Moray_House_School_of_Education_and_Spor/solution_weeks_9_10.xlsx
+++ b/multiSchoolOutput/01_Moray_House_School_of_Education_and_Spor/solution_weeks_9_10.xlsx
@@ -491,12 +491,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0335_01_1.1</t>
+          <t>0335_02_2.1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0335_02_2.1</t>
+          <t>0008_01_1.302</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -613,12 +613,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0335_02_2.1</t>
+          <t>0335_03_3.1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0001_01_1.275</t>
+          <t>0001_00_G.158</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -733,12 +733,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0201_02_2.07</t>
+          <t>0113_01_1.42</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -792,12 +792,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0001_02_2.343</t>
+          <t>0001_02_2.345</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -851,12 +851,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0209_-1_B.Z28</t>
+          <t>0228_-1_LG.07</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -910,12 +910,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0226_01_1.02</t>
+          <t>0450_01_1.50</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -927,7 +927,7 @@
         <v>50</v>
       </c>
       <c r="F9" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -969,12 +969,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0227_00_G.04</t>
+          <t>0310_00_G.Z02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0335_05_5.1</t>
+          <t>0113_01M_01M.467</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0001_00_G.158</t>
+          <t>0209_02_2.37</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0001_00_G.158</t>
+          <t>0335_04_4.1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1264,12 +1264,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0227_00_G.04</t>
+          <t>0310_00_G.Z02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0251_01_1.02</t>
+          <t>0113_01_1.434</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1441,12 +1441,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0335_01_1.3</t>
+          <t>0001_01_1.275</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0228_04_4.18</t>
+          <t>0335_02_2.1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1618,12 +1618,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0113_01_1.434</t>
+          <t>0251_01_1.01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1736,12 +1736,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0311_02_2.02</t>
+          <t>0227_01_1.06</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0001_00_G.158</t>
+          <t>0227_00_G.01</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0254_01_1.12</t>
+          <t>0113_01M_01M.474</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1972,12 +1972,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0335_02_2.3</t>
+          <t>0113_01_1.9</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0229_01_1.C</t>
+          <t>0229_01_1.B</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2090,12 +2090,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0112_-1_B.06</t>
+          <t>0335_01_1.1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2208,12 +2208,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR5</t>
+          <t>0214_00_G.23</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0201_02_2.11</t>
+          <t>0003_03_3.01</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2326,12 +2326,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0227_00_G.04</t>
+          <t>0001_00_G.159</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2343,7 +2343,7 @@
         <v>100</v>
       </c>
       <c r="F33" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2385,12 +2385,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0113_01_1.9</t>
+          <t>0335_02_2.3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0113_01M_01M.467</t>
+          <t>0112_-1_B.06</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2621,12 +2621,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0335_05_5.1</t>
+          <t>0335_02_2.1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0103_01_1.B19</t>
+          <t>0113_00_G.204</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0209_-1_B.Z28</t>
+          <t>0227_01_1.06</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0113_00_G.03</t>
+          <t>0335_05_5.3</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0113_01_1.26</t>
+          <t>0113_01M_01M.474</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3034,12 +3034,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0008_00_G.267</t>
+          <t>0001_00_G.158</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0001_01_1.276</t>
+          <t>0001_01_1.273</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0113_00_G.03</t>
+          <t>0201_02_2.12</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3405,7 +3405,7 @@
         <v>50</v>
       </c>
       <c r="F51" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -3447,12 +3447,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0209_02_2.37</t>
+          <t>0227_00_G.01</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0110_02_2.01</t>
+          <t>0335_05_5.1</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0310_00_G.Z02</t>
+          <t>0227_00_G.04</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3683,12 +3683,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0335_01_1.3</t>
+          <t>0001_01_1.275</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0113_03_3.3</t>
+          <t>0227_03_3.30</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3801,12 +3801,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0209_02_2.37</t>
+          <t>0335_04_4.1</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0201_02_2.07</t>
+          <t>0201_07_7.01</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3919,12 +3919,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0001_01_1.273</t>
+          <t>0311_02_2.01</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3978,12 +3978,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0113_00_G.200</t>
+          <t>0008_02_2.365</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4037,12 +4037,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0226_01_1.02</t>
+          <t>0335_05_5.3</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4096,12 +4096,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0228_04_4.18</t>
+          <t>0335_01_1.1</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0228_08_8.13</t>
+          <t>0228_11_11.01</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4172,7 +4172,7 @@
         <v>15</v>
       </c>
       <c r="F64" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0335_01_1.3</t>
+          <t>0335_04_4.1</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4391,12 +4391,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0450_04_4.35</t>
+          <t>0001_01_1.275</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0201_07_7.01</t>
+          <t>0201_01_1.01</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0227_02_2.13</t>
+          <t>0210_00-GFSSR4</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0113_01_1.42</t>
+          <t>0201_01_1.01</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0210_00_GFS2</t>
+          <t>0103_01_1.B10</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0113_01_1.9</t>
+          <t>0113_01_1.416</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4745,12 +4745,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR3</t>
+          <t>0254_01_1.5A</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4762,7 +4762,7 @@
         <v>5</v>
       </c>
       <c r="F74" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -4804,12 +4804,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0209_02_2.37</t>
+          <t>0001_00_G.158</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4863,12 +4863,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0113_00M_00M.03</t>
+          <t>0227_03_3.13</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0113_01M_01M.467</t>
+          <t>0110_02_2.01</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4981,12 +4981,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0335_05_5.1</t>
+          <t>0335_03_3.1</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR4</t>
+          <t>0113_03_3.3</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0228_04_4.18</t>
+          <t>0113_01M_01M.467</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0310_00_G.06</t>
+          <t>0201_01_1.02</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5175,7 +5175,7 @@
         <v>90</v>
       </c>
       <c r="F81" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -5217,12 +5217,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0450_04_4.35</t>
+          <t>0209_02_2.37</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5276,12 +5276,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0008_01_1.302</t>
+          <t>0335_03_3.1</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5335,12 +5335,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0008_-1_B.157</t>
+          <t>0201_02_2.11</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0335_03_3.1</t>
+          <t>0110_02_2.01</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5571,12 +5571,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0228_-1_LG.07</t>
+          <t>0227_01_1.06</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5630,12 +5630,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0335_02_2.1</t>
+          <t>0335_03_3.1</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0251_01_1.01</t>
+          <t>0113_01_1.434</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5748,12 +5748,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0450_04_4.35</t>
+          <t>0001_01_1.275</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0103_01_1.B04</t>
+          <t>0201_00_G.05</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5925,12 +5925,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR3</t>
+          <t>0450_02_2.63</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5942,7 +5942,7 @@
         <v>5</v>
       </c>
       <c r="F94" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0251_01_1.01</t>
+          <t>0008_-1_B.157</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0113_01_1.434</t>
+          <t>0201_02_2.11</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6107,7 +6107,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6220,12 +6220,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0227_00_G.01</t>
+          <t>0001_01_1.275</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0311_02_2.02</t>
+          <t>0228_-1_LG.07</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0228_04_4.18</t>
+          <t>0335_05_5.1</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0008_00_G.267</t>
+          <t>0001_00_G.158</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0228_04_4.18</t>
+          <t>0228_09_9.18</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -6515,12 +6515,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0201_07_7.01</t>
+          <t>0201_01_1.01</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -6574,12 +6574,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0201_05_5.01</t>
+          <t>0201_01_1.05</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6697,7 +6697,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0226_01_1.02</t>
+          <t>0113_00_G.03</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0335_04_4.1</t>
+          <t>0227_00_G.01</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0113_01M_01M.469</t>
+          <t>0103_03_3.D02</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0113_01M_01M.467</t>
+          <t>0228_04_4.18</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0450_04_4.35</t>
+          <t>0001_01_1.275</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -7105,12 +7105,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0210_00_GFSSR2</t>
+          <t>0450_01_1.63</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -7122,7 +7122,7 @@
         <v>5</v>
       </c>
       <c r="F114" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -7164,12 +7164,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0112_-1_B.02</t>
+          <t>0113_01_1.416</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -7223,12 +7223,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0219_00_G.02</t>
+          <t>0008_00_G.251</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -7282,12 +7282,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0113_01_1.434</t>
+          <t>0251_01_1.02</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -7341,12 +7341,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0227_03_3.13</t>
+          <t>0113_02M_02M.24</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0310_00_G.Z02</t>
+          <t>0227_00_G.04</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0113_00_G.10</t>
+          <t>0335_03_3.4</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -7476,7 +7476,7 @@
         <v>15</v>
       </c>
       <c r="F120" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -7518,12 +7518,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0227_00_G.01</t>
+          <t>0450_04_4.35</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -7582,7 +7582,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -7636,12 +7636,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0110_02_2.01</t>
+          <t>0113_01M_01M.467</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0008_00_G.267</t>
+          <t>0001_00_G.158</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0311_02_2.13</t>
+          <t>0201_01_1.02</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -7771,7 +7771,7 @@
         <v>80</v>
       </c>
       <c r="F125" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -7872,12 +7872,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0227_00_G.04</t>
+          <t>0310_00_G.Z02</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -7931,12 +7931,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0113_00_G.204</t>
+          <t>0113_01_1.42</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -7990,12 +7990,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0113_00_G.203</t>
+          <t>0103_01_1.B04</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0008_03_3.454</t>
+          <t>0209_-1_B.Z28</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -8108,12 +8108,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0335_02_2.1</t>
+          <t>0335_01_1.1</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -8167,12 +8167,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0335_03_3.1</t>
+          <t>0113_01M_01M.467</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0335_01_1.3</t>
+          <t>0001_00_G.158</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -8285,12 +8285,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0112_-1_B.06</t>
+          <t>0335_03_3.1</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -8344,12 +8344,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0450_04_4.35</t>
+          <t>0227_00_G.01</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0201_01_1.05</t>
+          <t>0103_01_1.B04</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -8462,12 +8462,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0209_02_2.37</t>
+          <t>0335_01_1.3</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -8521,12 +8521,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0003_00_G.02</t>
+          <t>0219_00_G.02</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0335_01_1.1</t>
+          <t>0110_02_2.01</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -8698,12 +8698,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>0219_00_G.02</t>
+          <t>0228_11_11.18</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -8762,7 +8762,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -8816,12 +8816,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0112_-1_B.06</t>
+          <t>0113_01M_01M.467</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0110_02_2.01</t>
+          <t>0112_-1_B.06</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0008_00_G.267</t>
+          <t>0335_04_4.1</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>0335_04_4.1</t>
+          <t>0450_04_4.35</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -9111,12 +9111,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>0335_05_5.3</t>
+          <t>0201_02_2.14</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -9128,7 +9128,7 @@
         <v>50</v>
       </c>
       <c r="F148" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -9170,12 +9170,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>0227_00_G.01</t>
+          <t>0001_01_1.275</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>0335_02_2.1</t>
+          <t>0008_01_1.302</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -9293,7 +9293,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -9347,12 +9347,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>0201_01_1.01</t>
+          <t>0210_00_GFS2</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -9406,12 +9406,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>0335_05_5.1</t>
+          <t>0228_09_9.18</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>0201_00_G.05</t>
+          <t>0113_00_G.203</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>0209_02_2.37</t>
+          <t>0335_01_1.3</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>0209_02_2.37</t>
+          <t>0335_04_4.1</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -9701,12 +9701,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>0001_00_G.158</t>
+          <t>0001_01_1.275</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -9760,12 +9760,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>0008_01_1.302</t>
+          <t>0335_05_5.1</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -9819,12 +9819,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>0201_00_G.05</t>
+          <t>0113_00_G.204</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>0450_04_4.35</t>
+          <t>0008_00_G.267</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>0335_01_1.1</t>
+          <t>0335_02_2.1</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>0335_04_4.1</t>
+          <t>0001_01_1.275</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -10055,12 +10055,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>0422_J_J.05</t>
+          <t>0311_02_2.02</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -10114,12 +10114,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>0103_01_1.B04</t>
+          <t>0201_05_5.01</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 10:00</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>0001_01_1.275</t>
+          <t>0335_01_1.3</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -10232,12 +10232,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>0110_02_2.01</t>
+          <t>0335_03_3.1</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>0001_01_1.275</t>
+          <t>0335_01_1.3</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>0422_J_J.05</t>
+          <t>0311_02_2.02</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -10409,12 +10409,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>0201_01_1.01</t>
+          <t>0003_00_G.01</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -10468,12 +10468,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>0228_-1_LG.07</t>
+          <t>0311_02_2.02</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -10527,12 +10527,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>0335_04_4.1</t>
+          <t>0001_01_1.275</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -10591,7 +10591,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -10645,12 +10645,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>0008_03_3.454</t>
+          <t>0228_-1_LG.07</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -10704,7 +10704,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>0335_05_5.1</t>
+          <t>0335_02_2.1</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>0450_04_4.35</t>
+          <t>0209_02_2.37</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -10822,12 +10822,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR3</t>
+          <t>0450_02_2.63</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -10839,7 +10839,7 @@
         <v>2</v>
       </c>
       <c r="F177" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
@@ -10881,12 +10881,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>0226_01_1.02</t>
+          <t>0335_05_5.3</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -10999,12 +10999,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>0227_00_G.01</t>
+          <t>0001_00_G.158</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -11058,12 +11058,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>0228_09_9.18</t>
+          <t>0008_01_1.302</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -11117,12 +11117,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>0209_-1_B.Z28</t>
+          <t>0227_01_1.06</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -11181,7 +11181,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>0201_07_7.01</t>
+          <t>0103_01_1.B19</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -11294,12 +11294,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>0227_02_2.29</t>
+          <t>0001_02_2.343</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -11311,7 +11311,7 @@
         <v>15</v>
       </c>
       <c r="F185" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
@@ -11353,12 +11353,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>0422_J_J.03</t>
+          <t>0209_-1_B.Z28</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -11412,12 +11412,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>0209_02_2.37</t>
+          <t>0227_00_G.01</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -11476,7 +11476,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -11530,12 +11530,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>0113_01_1.42</t>
+          <t>0113_00_G.203</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -11591,12 +11591,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>0335_00_G.12</t>
+          <t>0003_00_G.03</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -11608,7 +11608,7 @@
         <v>17</v>
       </c>
       <c r="F190" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
@@ -11652,12 +11652,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>0335_00_G.12</t>
+          <t>0201_02_2.06</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -11669,7 +11669,7 @@
         <v>17</v>
       </c>
       <c r="F191" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
@@ -11713,12 +11713,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>0227_03_3.30</t>
+          <t>0210_00-GFSSR4</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -11774,12 +11774,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>0335_05_5.1</t>
+          <t>0228_09_9.18</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -11835,12 +11835,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>0001_01_1.276</t>
+          <t>0001_01_1.274</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -11896,12 +11896,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>0335_00_G.12</t>
+          <t>0214_01_1.10</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -11913,7 +11913,7 @@
         <v>17</v>
       </c>
       <c r="F195" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
@@ -11957,7 +11957,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>0003_03_3.01</t>
+          <t>0201_02_2.11</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -12018,12 +12018,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>0335_02_2.4</t>
+          <t>0113_00_G.200</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -12079,12 +12079,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>0210_00_GFSSR2</t>
+          <t>0113_00_G.199</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -12096,7 +12096,7 @@
         <v>5</v>
       </c>
       <c r="F198" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
@@ -12140,12 +12140,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>0335_01_1.1</t>
+          <t>0335_02_2.1</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -12201,12 +12201,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>0008_00_G.267</t>
+          <t>0001_00_G.158</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -12262,12 +12262,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>0008_01_1.302</t>
+          <t>0112_-1_B.06</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -12323,12 +12323,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR3</t>
+          <t>0450_03_3.63</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -12340,7 +12340,7 @@
         <v>6</v>
       </c>
       <c r="F202" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
@@ -12384,12 +12384,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>0335_02_2.1</t>
+          <t>0112_-1_B.06</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -12450,7 +12450,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -12511,7 +12511,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -12567,12 +12567,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>0228_09_9.18</t>
+          <t>0113_01M_01M.467</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -12633,7 +12633,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -12689,12 +12689,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>0227_03_3.29</t>
+          <t>0001_02_2.349</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -12706,7 +12706,7 @@
         <v>15</v>
       </c>
       <c r="F208" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
@@ -12750,12 +12750,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>0335_01_1.3</t>
+          <t>0227_00_G.01</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -12811,12 +12811,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR3</t>
+          <t>0254_01_1.01</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -12828,7 +12828,7 @@
         <v>6</v>
       </c>
       <c r="F210" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
@@ -12872,12 +12872,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>0210_00_GFSSR2</t>
+          <t>0254_01_1.09</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -12889,7 +12889,7 @@
         <v>4</v>
       </c>
       <c r="F211" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>0228_07_7.18</t>
+          <t>0219_00_G.02</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -12994,7 +12994,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>0008_-1_B.157</t>
+          <t>0113_01_1.434</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>0228_11_11.18</t>
+          <t>0201_02_2.04</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -13116,12 +13116,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>0228_09_9.18</t>
+          <t>0335_03_3.1</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -13177,12 +13177,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>0103_01_1.B10</t>
+          <t>0201_05_5.01</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -13238,12 +13238,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>0113_02M_02M.24</t>
+          <t>0113_01M_01M.474</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>0008_01_1.302</t>
+          <t>0113_01M_01M.467</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -13365,7 +13365,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -13421,12 +13421,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>0008_01_1.302</t>
+          <t>0228_09_9.18</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -13482,12 +13482,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>0112_-1_B.06</t>
+          <t>0110_02_2.01</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>0228_09_9.18</t>
+          <t>0335_05_5.1</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -13665,12 +13665,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>0214_00_G.02</t>
+          <t>0113_01M_01M.469</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -13731,7 +13731,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -13792,7 +13792,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -13848,12 +13848,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>0335_03_3.1</t>
+          <t>0008_01_1.302</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -13909,12 +13909,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>0228_09_9.18</t>
+          <t>0110_02_2.01</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -13975,7 +13975,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -14031,12 +14031,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>0335_02_2.1</t>
+          <t>0335_05_5.1</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -14092,12 +14092,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>0227_00_G.01</t>
+          <t>0001_00_G.158</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -14153,12 +14153,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>0008_00_G.267</t>
+          <t>0450_04_4.35</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -14219,7 +14219,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 10:00</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -14275,12 +14275,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>0335_04_4.1</t>
+          <t>0335_01_1.3</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -14336,12 +14336,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>0008_01_1.302</t>
+          <t>0335_03_3.1</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -14397,12 +14397,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>0335_05_5.3</t>
+          <t>0226_04_4.04</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -14414,7 +14414,7 @@
         <v>50</v>
       </c>
       <c r="F236" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>0254_01_1.12</t>
+          <t>0227_03_3.30</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -14524,7 +14524,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -14585,7 +14585,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -14641,12 +14641,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>0214_00_G.23</t>
+          <t>0113_00M_00M.03</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -14702,12 +14702,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>0112_-1_B.06</t>
+          <t>0113_01M_01M.467</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -14763,12 +14763,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>0113_01M_01M.467</t>
+          <t>0335_05_5.1</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -14824,12 +14824,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>0228_11_11.11</t>
+          <t>0008_-1_B.154</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -14885,12 +14885,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>0335_01_1.1</t>
+          <t>0228_09_9.18</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -14946,12 +14946,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>0001_01_1.273</t>
+          <t>0001_01_1.274</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -15007,12 +15007,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>0113_01_1.9</t>
+          <t>0335_02_2.3</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -15068,12 +15068,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>0335_04_4.1</t>
+          <t>0008_00_G.267</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -15129,12 +15129,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>0001_00_G.158</t>
+          <t>0001_01_1.275</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -15190,12 +15190,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>0113_00_G.09</t>
+          <t>0300_00_NG.04</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -15207,7 +15207,7 @@
         <v>15</v>
       </c>
       <c r="F249" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G249" t="inlineStr">
         <is>
@@ -15251,12 +15251,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>0003_00_G.01</t>
+          <t>0103_01_1.B04</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -15312,12 +15312,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>0112_-1_B.06</t>
+          <t>0110_02_2.01</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -15378,7 +15378,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -15434,12 +15434,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>0110_02_2.01</t>
+          <t>0113_01M_01M.467</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -15495,12 +15495,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>0335_03_3.4</t>
+          <t>0001_02_2.347</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -15556,7 +15556,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>0008_-1_B.157</t>
+          <t>0003_03_3.01</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -15617,12 +15617,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>0335_03_3.1</t>
+          <t>0228_09_9.18</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -15678,12 +15678,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>0335_04_4.3</t>
+          <t>0311_02_2.02</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -15800,12 +15800,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>0113_01M_01M.467</t>
+          <t>0008_01_1.302</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -15861,12 +15861,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>0112_-1_B.06</t>
+          <t>0113_01M_01M.467</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -15927,7 +15927,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -15983,12 +15983,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>0110_02_2.01</t>
+          <t>0335_01_1.1</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -16044,12 +16044,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>0201_01_1.05</t>
+          <t>0103_01_1.B10</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -16105,12 +16105,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>0227_03_3.14</t>
+          <t>0335_02_2.18</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -16122,7 +16122,7 @@
         <v>15</v>
       </c>
       <c r="F264" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G264" t="inlineStr">
         <is>
@@ -16171,7 +16171,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -16227,12 +16227,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>0008_01_1.302</t>
+          <t>0110_02_2.01</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -16293,7 +16293,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -16349,12 +16349,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>0003_00_G.01</t>
+          <t>0201_02_2.07</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -16415,7 +16415,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -16471,12 +16471,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>0335_05_5.3</t>
+          <t>0450_01_1.40</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -16488,7 +16488,7 @@
         <v>50</v>
       </c>
       <c r="F270" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G270" t="inlineStr">
         <is>
@@ -16532,12 +16532,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>0001_01_1.274</t>
+          <t>0001_01_1.273</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>0335_04_4.1</t>
+          <t>0450_04_4.35</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -16654,12 +16654,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>0201_02_2.07</t>
+          <t>0214_01_1.01</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -16715,12 +16715,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>0450_04_4.35</t>
+          <t>0335_04_4.1</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -16776,12 +16776,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>0310_00_G.06</t>
+          <t>0201_01_1.02</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -16793,7 +16793,7 @@
         <v>90</v>
       </c>
       <c r="F275" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -16837,12 +16837,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>0335_02_2.1</t>
+          <t>0228_09_9.18</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -16898,12 +16898,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>0227_01_1.06</t>
+          <t>0008_03_3.454</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -16964,7 +16964,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -17020,12 +17020,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>0335_02_2.1</t>
+          <t>0335_01_1.1</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -17086,7 +17086,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -17142,12 +17142,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>0335_03_3.1</t>
+          <t>0228_09_9.18</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -17203,12 +17203,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>0110_02_2.02</t>
+          <t>0228_09_9.01</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -17220,7 +17220,7 @@
         <v>15</v>
       </c>
       <c r="F282" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G282" t="inlineStr">
         <is>
@@ -17264,12 +17264,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>0214_00_G.02</t>
+          <t>0113_01_1.9</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -17330,7 +17330,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -17386,7 +17386,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>0008_01_1.302</t>
+          <t>0335_01_1.1</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -17447,7 +17447,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>0008_-1_B.154</t>
+          <t>0335_01_1.4</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -17464,7 +17464,7 @@
         <v>15</v>
       </c>
       <c r="F286" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G286" t="inlineStr">
         <is>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>0335_03_3.1</t>
+          <t>0335_05_5.1</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -17569,12 +17569,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>0228_-1_LG.06</t>
+          <t>0113_00M_00M.05</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -17630,7 +17630,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>0227_00_G.01</t>
+          <t>0450_04_4.35</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -17752,12 +17752,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>0003_03_3.01</t>
+          <t>0113_01_1.434</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -17813,12 +17813,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>0003_01_1.03</t>
+          <t>0003_01_1.02</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -17874,12 +17874,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>0103_01_1.B04</t>
+          <t>0103_01_1.B10</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -17935,12 +17935,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>0201_05_5.01</t>
+          <t>0201_07_7.01</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -17996,12 +17996,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>0210_00_GFSSR2</t>
+          <t>0450_01_1.63</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -18013,7 +18013,7 @@
         <v>6</v>
       </c>
       <c r="F295" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G295" t="inlineStr">
         <is>
@@ -18057,12 +18057,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>0254_01_1.10</t>
+          <t>0311_04_4.08</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -18118,12 +18118,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>0335_02_2.1</t>
+          <t>0112_-1_B.06</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -18179,12 +18179,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>0113_00_G.204</t>
+          <t>0201_00_G.05</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -18245,7 +18245,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -18301,12 +18301,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>0210_00_GFS2</t>
+          <t>0113_00_G.204</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -18362,12 +18362,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>0113_00_G.11</t>
+          <t>0219_00_G.01</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -18379,7 +18379,7 @@
         <v>15</v>
       </c>
       <c r="F301" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G301" t="inlineStr">
         <is>
@@ -18428,7 +18428,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -18489,7 +18489,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -18545,12 +18545,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>0335_01_1.1</t>
+          <t>0335_03_3.1</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -18606,12 +18606,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>0214_00_G.02</t>
+          <t>0113_01_1.416</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -18667,12 +18667,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>0228_08_8.16</t>
+          <t>0113_00_G.11</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -18728,12 +18728,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>0110_02_2.02</t>
+          <t>0001_02_2.343</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -18745,7 +18745,7 @@
         <v>15</v>
       </c>
       <c r="F307" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G307" t="inlineStr">
         <is>
@@ -18789,12 +18789,12 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>0110_02_2.01</t>
+          <t>0335_05_5.1</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -18855,7 +18855,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -18911,12 +18911,12 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>0228_08_8.13</t>
+          <t>0113_00_G.12</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -18972,12 +18972,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>0103_01_1.B19</t>
+          <t>0113_01_1.42</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -19033,12 +19033,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>0228_04_4.18</t>
+          <t>0110_02_2.01</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -19094,7 +19094,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>0228_09_9.18</t>
+          <t>0335_01_1.1</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -19155,12 +19155,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>0228_04_4.18</t>
+          <t>0335_05_5.1</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -19221,7 +19221,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -19277,12 +19277,12 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>0311_02_2.01</t>
+          <t>0001_01_1.265</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -19338,12 +19338,12 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>0008_00_G.267</t>
+          <t>0209_02_2.37</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -19399,12 +19399,12 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>0103_01_1.B19</t>
+          <t>0103_01_1.B04</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -19460,12 +19460,12 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>0110_02_2.01</t>
+          <t>0335_05_5.1</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -19521,12 +19521,12 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>0008_01_1.302</t>
+          <t>0335_05_5.1</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -19582,12 +19582,12 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>0003_00_G.01</t>
+          <t>0210_00_GFS2</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -19648,7 +19648,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Friday 10:00</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -19704,12 +19704,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>0113_00_G.203</t>
+          <t>0201_05_5.01</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -19765,12 +19765,12 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>0335_04_4.1</t>
+          <t>0450_04_4.35</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -19826,7 +19826,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>0003_01_1.02</t>
+          <t>0113_02_2.36</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -19887,12 +19887,12 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>0103_01_1.B10</t>
+          <t>0214_01_1.01</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -19953,7 +19953,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -20009,12 +20009,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>0201_00_G.05</t>
+          <t>0003_00_G.01</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -20070,12 +20070,12 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>0335_03_3.1</t>
+          <t>0112_-1_B.06</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -20131,12 +20131,12 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>0214_01_1.01</t>
+          <t>0003_00_G.01</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -20192,12 +20192,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>0001_00_G.158</t>
+          <t>0001_01_1.275</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -20253,12 +20253,12 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>0112_00_G.02</t>
+          <t>0112_00_G.01</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -20319,7 +20319,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -20380,7 +20380,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -20436,12 +20436,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>0113_00_G.203</t>
+          <t>0103_01_1.B10</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -20502,7 +20502,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -20563,7 +20563,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -20624,7 +20624,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -20680,12 +20680,12 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>0227_01_1.06</t>
+          <t>0228_-1_LG.07</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -20741,12 +20741,12 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>0335_02_2.1</t>
+          <t>0008_01_1.302</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -20802,12 +20802,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>0228_09_9.18</t>
+          <t>0335_02_2.1</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -20868,7 +20868,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -20924,12 +20924,12 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>0112_-1_B.06</t>
+          <t>0228_04_4.18</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -20985,12 +20985,12 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>0335_01_1.1</t>
+          <t>0008_01_1.302</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -21051,7 +21051,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -21107,12 +21107,12 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>0310_00_G.06</t>
+          <t>0201_01_1.02</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -21124,7 +21124,7 @@
         <v>90</v>
       </c>
       <c r="F346" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G346" t="inlineStr">
         <is>
@@ -21168,12 +21168,12 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>0112_-1_B.06</t>
+          <t>0110_02_2.01</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -21229,12 +21229,12 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>0251_01_1.01</t>
+          <t>0008_-1_B.157</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -21290,12 +21290,12 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>0335_01_1.3</t>
+          <t>0227_00_G.01</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -21351,12 +21351,12 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>0113_01M_01M.467</t>
+          <t>0008_01_1.302</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -21412,12 +21412,12 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>0210_00_GFSSR2</t>
+          <t>0450_01_1.63</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -21429,7 +21429,7 @@
         <v>6</v>
       </c>
       <c r="F351" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G351" t="inlineStr">
         <is>
@@ -21473,12 +21473,12 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>0201_02_2.11</t>
+          <t>0003_03_3.01</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -21539,7 +21539,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -21595,12 +21595,12 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>0113_01M_01M.467</t>
+          <t>0110_02_2.01</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -21656,12 +21656,12 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>0335_01_1.3</t>
+          <t>0209_02_2.37</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -21722,7 +21722,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -21778,7 +21778,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>0228_-1_LG.08</t>
+          <t>0228_-1_LG.10</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -21839,12 +21839,12 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>0310_00_G.Z02</t>
+          <t>0227_00_G.04</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -21900,12 +21900,12 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>0228_09_9.18</t>
+          <t>0335_05_5.1</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -21966,7 +21966,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -22027,7 +22027,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -22083,12 +22083,12 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>0201_07_7.14</t>
+          <t>0227_03_3.54</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -22144,12 +22144,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>0103_01_1.B19</t>
+          <t>0003_00_G.01</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -22266,12 +22266,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>0201_01_1.05</t>
+          <t>0201_05_5.01</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -22327,12 +22327,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>0335_01_1.1</t>
+          <t>0335_05_5.1</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -22388,12 +22388,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>0214_01_1.01</t>
+          <t>0113_00_G.203</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -22454,7 +22454,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -22510,12 +22510,12 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>0113_01M_01M.467</t>
+          <t>0335_05_5.1</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -22571,12 +22571,12 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>0227_02_2.13</t>
+          <t>0113_01M_01M.474</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -22637,7 +22637,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -22693,12 +22693,12 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>0103_01_1.B10</t>
+          <t>0201_02_2.07</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -22754,12 +22754,12 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>0227_01_1.02</t>
+          <t>0335_03_3.3</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -22815,12 +22815,12 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>0228_04_4.18</t>
+          <t>0335_02_2.1</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -22876,12 +22876,12 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>0228_04_4.18</t>
+          <t>0113_01M_01M.467</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -22942,7 +22942,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -22998,12 +22998,12 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>0209_02_2.37</t>
+          <t>0008_00_G.267</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -23059,12 +23059,12 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>0335_03_3.1</t>
+          <t>0335_02_2.1</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -23120,12 +23120,12 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>0251_01_1.02</t>
+          <t>0113_01_1.434</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -23181,12 +23181,12 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>0003_00_G.01</t>
+          <t>0214_01_1.01</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -23242,12 +23242,12 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>0335_01_1.3</t>
+          <t>0335_04_4.1</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -23303,12 +23303,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>0229_01_1.B</t>
+          <t>0229_01_1.C</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -23364,12 +23364,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>0201_07_7.14</t>
+          <t>0227_02_2.54</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -23425,12 +23425,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>0228_-1_LG.07</t>
+          <t>0311_02_2.02</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -23486,12 +23486,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>0209_-1_B.Z28</t>
+          <t>0227_01_1.06</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -23547,12 +23547,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>0310_00_G.Z02</t>
+          <t>0227_00_G.04</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -23608,12 +23608,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>0103_01_1.B10</t>
+          <t>0201_01_1.05</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -23669,12 +23669,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>0227_03_3.29</t>
+          <t>0311_04_4.09</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -23686,7 +23686,7 @@
         <v>15</v>
       </c>
       <c r="F388" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G388" t="inlineStr">
         <is>
@@ -23730,12 +23730,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>0228_13_13.07</t>
+          <t>0008_00_G.252</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -23747,7 +23747,7 @@
         <v>15</v>
       </c>
       <c r="F389" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G389" t="inlineStr">
         <is>
@@ -23791,12 +23791,12 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>0110_02_2.01</t>
+          <t>0228_04_4.18</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -23857,7 +23857,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -23918,7 +23918,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -23979,7 +23979,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -24040,7 +24040,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -24096,12 +24096,12 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>0110_02_2.01</t>
+          <t>0113_01M_01M.467</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -24157,12 +24157,12 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>0254_01_1.09</t>
+          <t>0450_02_2.63</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -24223,7 +24223,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -24279,12 +24279,12 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>0335_01_1.1</t>
+          <t>0112_-1_B.06</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -24340,12 +24340,12 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>0310_00_G.06</t>
+          <t>0201_01_1.02</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
@@ -24357,7 +24357,7 @@
         <v>90</v>
       </c>
       <c r="F399" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G399" t="inlineStr">
         <is>
@@ -24406,7 +24406,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -24462,12 +24462,12 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>0214_00_G.23</t>
+          <t>0113_01M_01M.474</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
@@ -24523,12 +24523,12 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>0228_09_9.18</t>
+          <t>0335_03_3.1</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
@@ -24584,12 +24584,12 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>0110_02_2.01</t>
+          <t>0335_03_3.1</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -24645,12 +24645,12 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>0113_01_1.434</t>
+          <t>0251_01_1.02</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
@@ -24711,7 +24711,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -24767,12 +24767,12 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>0209_02_2.37</t>
+          <t>0001_01_1.275</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -24828,12 +24828,12 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>0001_01_1.266</t>
+          <t>0219_00_G.02</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -24889,12 +24889,12 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>0335_04_4.3</t>
+          <t>0311_02_2.02</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -24950,7 +24950,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>0003_03_3.01</t>
+          <t>0201_02_2.11</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -25011,12 +25011,12 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>0335_01_1.1</t>
+          <t>0335_03_3.1</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -25077,7 +25077,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -25138,7 +25138,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -25199,7 +25199,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -25255,12 +25255,12 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>0335_05_5.1</t>
+          <t>0335_02_2.1</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -25316,12 +25316,12 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>0113_00_G.10</t>
+          <t>0227_02_2.14</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -25377,12 +25377,12 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>0227_00_G.01</t>
+          <t>0001_00_G.158</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -25438,12 +25438,12 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>0335_03_3.1</t>
+          <t>0335_02_2.1</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -25504,7 +25504,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -25560,12 +25560,12 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>0001_00_G.158</t>
+          <t>0335_01_1.3</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
@@ -25621,12 +25621,12 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>0001_01_1.275</t>
+          <t>0227_00_G.01</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -25682,12 +25682,12 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>0112_-1_B.06</t>
+          <t>0335_05_5.1</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
@@ -25743,12 +25743,12 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>0227_03_3.13</t>
+          <t>0113_00M_00M.07</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
@@ -25804,12 +25804,12 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>0450_04_4.35</t>
+          <t>0335_04_4.1</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -25865,12 +25865,12 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>0214_01_1.01</t>
+          <t>0003_00_G.01</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
@@ -25931,7 +25931,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -25987,12 +25987,12 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>0003_00_G.01</t>
+          <t>0210_00_GFS2</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -26048,12 +26048,12 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>0110_02_2.01</t>
+          <t>0112_-1_B.06</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -26109,12 +26109,12 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>0229_01_1.B</t>
+          <t>0229_01_1.C</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -26175,7 +26175,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
@@ -26236,7 +26236,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -26292,12 +26292,12 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR3</t>
+          <t>0450_03_3.42</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
@@ -26309,7 +26309,7 @@
         <v>5</v>
       </c>
       <c r="F431" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G431" t="inlineStr">
         <is>
@@ -26353,12 +26353,12 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>0103_01_1.B04</t>
+          <t>0113_01_1.42</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -26414,12 +26414,12 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>0228_09_9.18</t>
+          <t>0110_02_2.01</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -26475,12 +26475,12 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>0335_05_5.1</t>
+          <t>0335_01_1.1</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -26536,12 +26536,12 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>0214_00_G.22</t>
+          <t>0227_02_2.39</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -26597,12 +26597,12 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>0226_01_1.02</t>
+          <t>0450_02_2.20</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -26614,7 +26614,7 @@
         <v>50</v>
       </c>
       <c r="F436" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G436" t="inlineStr">
         <is>
@@ -26658,12 +26658,12 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>0201_02_2.07</t>
+          <t>0103_01_1.B19</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -26719,12 +26719,12 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>0335_01_1.1</t>
+          <t>0335_02_2.1</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
@@ -26785,7 +26785,7 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
@@ -26846,7 +26846,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
@@ -26902,12 +26902,12 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>0008_01_1.302</t>
+          <t>0335_01_1.1</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
@@ -26963,12 +26963,12 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>0001_01_1.270</t>
+          <t>0001_02_2.349</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
@@ -27024,12 +27024,12 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>0227_02_2.14</t>
+          <t>0001_02_2.347</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
@@ -27041,7 +27041,7 @@
         <v>15</v>
       </c>
       <c r="F443" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G443" t="inlineStr">
         <is>
@@ -27085,12 +27085,12 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>0201_02_2.11</t>
+          <t>0251_01_1.01</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
@@ -27146,12 +27146,12 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>0227_01_1.02</t>
+          <t>0335_03_3.2</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -27207,12 +27207,12 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>0335_05_5.1</t>
+          <t>0113_01M_01M.467</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
@@ -27268,12 +27268,12 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>0335_05_5.1</t>
+          <t>0228_09_9.18</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -27329,12 +27329,12 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>0310_00_G.06</t>
+          <t>0201_01_1.02</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
@@ -27346,7 +27346,7 @@
         <v>90</v>
       </c>
       <c r="F448" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G448" t="inlineStr">
         <is>
@@ -27390,12 +27390,12 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>0335_04_4.3</t>
+          <t>0422_J_J.03</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
@@ -27451,12 +27451,12 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>0335_03_3.1</t>
+          <t>0112_-1_B.06</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
@@ -27512,7 +27512,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>0201_05_5.07</t>
+          <t>0001_01_1.270</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -27529,7 +27529,7 @@
         <v>15</v>
       </c>
       <c r="F451" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G451" t="inlineStr">
         <is>
@@ -27573,12 +27573,12 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>0335_03_3.1</t>
+          <t>0228_04_4.18</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
@@ -27634,7 +27634,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>0228_13_13.07</t>
+          <t>0335_02_2.18</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -27651,7 +27651,7 @@
         <v>15</v>
       </c>
       <c r="F453" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G453" t="inlineStr">
         <is>
@@ -27695,12 +27695,12 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>0113_00_G.204</t>
+          <t>0210_00_GFS2</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
@@ -27756,12 +27756,12 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>0112_00_G.01</t>
+          <t>0112_00_G.02</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
@@ -27817,12 +27817,12 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>0227_00_G.01</t>
+          <t>0008_00_G.267</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
@@ -27878,12 +27878,12 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>0112_-1_B.06</t>
+          <t>0335_02_2.1</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
@@ -27939,12 +27939,12 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>0219_00_G.02</t>
+          <t>0003_00_G.02</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
@@ -28000,12 +28000,12 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>0210_00_GFS2</t>
+          <t>0201_00_G.05</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
@@ -28061,12 +28061,12 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>0001_01_1.274</t>
+          <t>0001_01_1.276</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>0228_09_9.18</t>
+          <t>0112_-1_B.06</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -28183,12 +28183,12 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>0219_00_G.01</t>
+          <t>0008_00_G.252</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
@@ -28249,7 +28249,7 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
@@ -28305,12 +28305,12 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>0228_04_4.18</t>
+          <t>0335_01_1.1</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
@@ -28366,12 +28366,12 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>0113_00_G.11</t>
+          <t>0228_08_8.13</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
@@ -28427,12 +28427,12 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>0201_05_5.01</t>
+          <t>0003_00_G.01</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
@@ -28488,12 +28488,12 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>0001_01_1.275</t>
+          <t>0335_01_1.3</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
@@ -28549,12 +28549,12 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>0227_00_G.04</t>
+          <t>0310_00_G.Z02</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
@@ -28610,12 +28610,12 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>0001_01_1.276</t>
+          <t>0001_01_1.273</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
@@ -28671,12 +28671,12 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>0113_01M_01M.467</t>
+          <t>0228_04_4.18</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
@@ -28732,12 +28732,12 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>0228_11_11.11</t>
+          <t>0008_02_2.365</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
@@ -28749,7 +28749,7 @@
         <v>15</v>
       </c>
       <c r="F471" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G471" t="inlineStr">
         <is>
@@ -28793,12 +28793,12 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>0008_01_1.302</t>
+          <t>0112_-1_B.06</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
@@ -28854,12 +28854,12 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>0201_01_1.05</t>
+          <t>0201_05_5.01</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
@@ -28915,12 +28915,12 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>0110_02_2.01</t>
+          <t>0335_01_1.1</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
@@ -28976,12 +28976,12 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>0311_02_2.01</t>
+          <t>0001_01_1.274</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
@@ -29042,7 +29042,7 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
@@ -29098,12 +29098,12 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>0113_01_1.42</t>
+          <t>0103_01_1.B19</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
@@ -29159,12 +29159,12 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>0113_01M_01M.467</t>
+          <t>0228_04_4.18</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
@@ -29220,12 +29220,12 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>0210_00_GFSSR2</t>
+          <t>0254_01_1.5A</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
@@ -29237,7 +29237,7 @@
         <v>2</v>
       </c>
       <c r="F479" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G479" t="inlineStr">
         <is>
@@ -29281,12 +29281,12 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>0113_01_1.42</t>
+          <t>0113_00_G.203</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
@@ -29342,12 +29342,12 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>0001_01_1.275</t>
+          <t>0450_04_4.35</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
@@ -29403,12 +29403,12 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>0113_00_G.12</t>
+          <t>0227_03_3.14</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
@@ -29464,12 +29464,12 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>0201_00_G.05</t>
+          <t>0113_00_G.203</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>0112_-1_B.06</t>
+          <t>0335_03_3.1</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
@@ -29586,12 +29586,12 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>0227_02_2.29</t>
+          <t>0254_01_1.08</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
@@ -29603,7 +29603,7 @@
         <v>15</v>
       </c>
       <c r="F485" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G485" t="inlineStr">
         <is>
@@ -29647,12 +29647,12 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>0228_04_4.18</t>
+          <t>0008_01_1.302</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
@@ -29713,7 +29713,7 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
@@ -29769,12 +29769,12 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>0335_01_1.3</t>
+          <t>0001_00_G.158</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
@@ -29835,7 +29835,7 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
@@ -29891,12 +29891,12 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>0210_00_GFSSR2</t>
+          <t>0254_01_1.5A</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
@@ -29908,7 +29908,7 @@
         <v>6</v>
       </c>
       <c r="F490" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G490" t="inlineStr">
         <is>
@@ -30013,12 +30013,12 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>0201_02_2.06</t>
+          <t>0201_07_7.14</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
@@ -30074,12 +30074,12 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>0008_00_G.267</t>
+          <t>0209_02_2.37</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
@@ -30135,12 +30135,12 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>0228_13_13.07</t>
+          <t>0008_-1_B.153</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
@@ -30201,7 +30201,7 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
@@ -30262,7 +30262,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
@@ -30318,12 +30318,12 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>0112_-1_B.06</t>
+          <t>0008_01_1.302</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
@@ -30379,12 +30379,12 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>0227_00_G.01</t>
+          <t>0001_01_1.275</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
@@ -30440,12 +30440,12 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>0335_05_5.1</t>
+          <t>0112_-1_B.06</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
@@ -30501,12 +30501,12 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>0214_00_G.22</t>
+          <t>0227_03_3.54</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
@@ -30562,12 +30562,12 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>0201_01_1.05</t>
+          <t>0210_00_GFS2</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
@@ -30623,12 +30623,12 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>0008_00_G.267</t>
+          <t>0001_01_1.275</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
@@ -30684,12 +30684,12 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>0113_01M_01M.467</t>
+          <t>0335_01_1.1</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
@@ -30745,12 +30745,12 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>0254_01_1.10</t>
+          <t>0201_07_7.02</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
@@ -30806,12 +30806,12 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>0110_02_2.01</t>
+          <t>0008_01_1.302</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
@@ -30867,12 +30867,12 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>0311_02_2.02</t>
+          <t>0209_-1_B.Z28</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
@@ -30928,12 +30928,12 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>0335_05_5.1</t>
+          <t>0335_02_2.1</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
@@ -30989,12 +30989,12 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>0210_00_GFSSR2</t>
+          <t>0450_03_3.63</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
@@ -31006,7 +31006,7 @@
         <v>6</v>
       </c>
       <c r="F508" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G508" t="inlineStr">
         <is>
@@ -31050,12 +31050,12 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>0335_05_5.1</t>
+          <t>0228_04_4.18</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
@@ -31111,12 +31111,12 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>0214_01_1.01</t>
+          <t>0113_01_1.42</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
@@ -31172,12 +31172,12 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>0001_01_1.275</t>
+          <t>0209_02_2.37</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
@@ -31233,12 +31233,12 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>0001_01_1.275</t>
+          <t>0450_04_4.35</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
@@ -31299,7 +31299,7 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
@@ -31360,7 +31360,7 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
@@ -31416,12 +31416,12 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>0201_01_1.01</t>
+          <t>0201_02_2.07</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
@@ -31477,12 +31477,12 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>0110_02_2.02</t>
+          <t>0201_05_5.07</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
@@ -31538,12 +31538,12 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>0113_00_G.203</t>
+          <t>0103_01_1.B10</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
@@ -31599,12 +31599,12 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR4</t>
+          <t>0113_01M_01M.474</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
@@ -31660,12 +31660,12 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>0201_01_1.06</t>
+          <t>0201_01_1.08</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
@@ -31677,7 +31677,7 @@
         <v>275</v>
       </c>
       <c r="F519" t="n">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="G519" t="inlineStr">
         <is>
@@ -31719,12 +31719,12 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>0003_00_G.01</t>
+          <t>0113_00_G.204</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
@@ -31780,12 +31780,12 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>0311_02_2.01</t>
+          <t>0001_01_1.274</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
@@ -31902,12 +31902,12 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>0228_09_9.18</t>
+          <t>0335_05_5.1</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
@@ -31963,12 +31963,12 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>0201_02_2.07</t>
+          <t>0214_01_1.01</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">

--- a/multiSchoolOutput/01_Moray_House_School_of_Education_and_Spor/solution_weeks_9_10.xlsx
+++ b/multiSchoolOutput/01_Moray_House_School_of_Education_and_Spor/solution_weeks_9_10.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0335_02_2.1</t>
+          <t>0201_02_2.11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -508,7 +508,7 @@
         <v>25</v>
       </c>
       <c r="F2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -552,12 +552,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0008_01_1.302</t>
+          <t>0228_04_4.18</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -613,12 +613,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0335_03_3.1</t>
+          <t>0251_01_1.02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -630,7 +630,7 @@
         <v>25</v>
       </c>
       <c r="F4" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -674,12 +674,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0001_00_G.158</t>
+          <t>0335_01_1.9</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -691,7 +691,7 @@
         <v>30</v>
       </c>
       <c r="F5" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -733,12 +733,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0113_01_1.42</t>
+          <t>0201_05_5.01</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Friday 10:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -792,12 +792,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0001_02_2.345</t>
+          <t>0001_02_2.343</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -851,12 +851,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0228_-1_LG.07</t>
+          <t>0335_04_4.3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -910,12 +910,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0450_01_1.50</t>
+          <t>0201_05_5.05</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -927,7 +927,7 @@
         <v>50</v>
       </c>
       <c r="F9" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -969,12 +969,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0310_00_G.Z02</t>
+          <t>0227_00_G.04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tuesday 16:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0113_01M_01M.467</t>
+          <t>0110_02_2.01</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0209_02_2.37</t>
+          <t>0335_01_1.9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1104,7 +1104,7 @@
         <v>30</v>
       </c>
       <c r="F12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0335_04_4.1</t>
+          <t>0335_01_1.9</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1163,7 +1163,7 @@
         <v>30</v>
       </c>
       <c r="F13" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0003_03_3.01</t>
+          <t>0113_01_1.434</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1264,12 +1264,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0310_00_G.Z02</t>
+          <t>0227_00_G.04</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Friday 13:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0113_01_1.434</t>
+          <t>0008_-1_B.157</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1382,12 +1382,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0209_02_2.37</t>
+          <t>0335_05_5.2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1399,7 +1399,7 @@
         <v>30</v>
       </c>
       <c r="F17" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0001_01_1.275</t>
+          <t>0335_00_G.10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1458,7 +1458,7 @@
         <v>30</v>
       </c>
       <c r="F18" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1500,12 +1500,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0335_02_2.1</t>
+          <t>0251_01_1.01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1517,7 +1517,7 @@
         <v>25</v>
       </c>
       <c r="F19" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1559,12 +1559,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0008_00_G.267</t>
+          <t>0335_05_5.2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1576,7 +1576,7 @@
         <v>30</v>
       </c>
       <c r="F20" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1618,12 +1618,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0251_01_1.01</t>
+          <t>0003_03_3.01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Monday 11:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1736,12 +1736,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0227_01_1.06</t>
+          <t>0311_02_2.02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0209_01_1.21</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1812,7 +1812,7 @@
         <v>125</v>
       </c>
       <c r="F24" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1854,12 +1854,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0227_00_G.01</t>
+          <t>0335_04_4.2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1871,7 +1871,7 @@
         <v>30</v>
       </c>
       <c r="F25" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1972,12 +1972,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0113_01_1.9</t>
+          <t>0113_01M_01M.469</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2090,12 +2090,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0335_01_1.1</t>
+          <t>0335_05_5.1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0003_01_1.01</t>
+          <t>0450_03_3.52</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2166,7 +2166,7 @@
         <v>23</v>
       </c>
       <c r="F30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0214_00_G.23</t>
+          <t>0113_01M_01M.20</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2225,7 +2225,7 @@
         <v>10</v>
       </c>
       <c r="F31" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2267,12 +2267,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0003_03_3.01</t>
+          <t>0008_-1_B.157</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2326,12 +2326,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0001_00_G.159</t>
+          <t>0227_00_G.04</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2343,7 +2343,7 @@
         <v>100</v>
       </c>
       <c r="F33" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2385,12 +2385,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0335_02_2.3</t>
+          <t>0113_01_1.416</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Friday 12:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Thursday 15:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2520,7 +2520,7 @@
         <v>120</v>
       </c>
       <c r="F36" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2562,12 +2562,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0112_-1_B.06</t>
+          <t>0335_05_5.1</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2621,12 +2621,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0335_02_2.1</t>
+          <t>0110_02_2.01</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0113_00_G.204</t>
+          <t>0001_01_1.274</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2697,7 +2697,7 @@
         <v>20</v>
       </c>
       <c r="F39" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2739,12 +2739,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0227_01_1.06</t>
+          <t>0008_03_3.454</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0335_05_5.3</t>
+          <t>0113_00_G.03</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Wednesday 16:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0226_01_1.02</t>
+          <t>0113_00_G.03</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0113_01M_01M.474</t>
+          <t>0450_03_3.62</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2992,7 +2992,7 @@
         <v>10</v>
       </c>
       <c r="F44" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -3034,12 +3034,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0001_00_G.158</t>
+          <t>0335_01_1.9</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3051,7 +3051,7 @@
         <v>30</v>
       </c>
       <c r="F45" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0003_01_1.01</t>
+          <t>0113_02_2.36</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3287,7 +3287,7 @@
         <v>23</v>
       </c>
       <c r="F49" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -3329,12 +3329,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0008_-1_B.157</t>
+          <t>0251_01_1.01</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0201_02_2.12</t>
+          <t>0201_05_5.05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3405,7 +3405,7 @@
         <v>50</v>
       </c>
       <c r="F51" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -3447,12 +3447,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0227_00_G.01</t>
+          <t>0335_04_4.2</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3464,7 +3464,7 @@
         <v>30</v>
       </c>
       <c r="F52" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -3506,12 +3506,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0335_05_5.1</t>
+          <t>0228_09_9.18</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Friday 16:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3641,7 +3641,7 @@
         <v>120</v>
       </c>
       <c r="F55" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -3683,12 +3683,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0001_01_1.275</t>
+          <t>0335_05_5.2</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3700,7 +3700,7 @@
         <v>30</v>
       </c>
       <c r="F56" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -3742,12 +3742,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0227_03_3.30</t>
+          <t>0113_03_3.3</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3801,12 +3801,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0335_04_4.1</t>
+          <t>0335_01_1.9</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3818,7 +3818,7 @@
         <v>30</v>
       </c>
       <c r="F58" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -3860,12 +3860,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0201_07_7.01</t>
+          <t>0214_01_1.01</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3919,12 +3919,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0311_02_2.01</t>
+          <t>0001_01_1.276</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3978,12 +3978,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0008_02_2.365</t>
+          <t>0311_04_4.09</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Thursday 11:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4096,12 +4096,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0335_01_1.1</t>
+          <t>0228_09_9.18</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0228_11_11.01</t>
+          <t>0008_00_G.252</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Wednesday 14:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4231,7 +4231,7 @@
         <v>120</v>
       </c>
       <c r="F65" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Friday 16:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0335_04_4.1</t>
+          <t>0113_00M_00M.05</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Friday 10:00</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4349,7 +4349,7 @@
         <v>30</v>
       </c>
       <c r="F67" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -4391,12 +4391,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0001_01_1.275</t>
+          <t>0112_-1_B.01</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4408,7 +4408,7 @@
         <v>30</v>
       </c>
       <c r="F68" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -4450,12 +4450,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0201_01_1.01</t>
+          <t>0214_01_1.01</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR4</t>
+          <t>0113_01_1.26</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0201_01_1.01</t>
+          <t>0201_05_5.01</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0103_01_1.B10</t>
+          <t>0210_00_GFS2</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0113_01_1.416</t>
+          <t>0103_03_3.D02</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0254_01_1.5A</t>
+          <t>0450_01_1.62</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4762,7 +4762,7 @@
         <v>5</v>
       </c>
       <c r="F74" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -4804,12 +4804,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0001_00_G.158</t>
+          <t>0335_05_5.2</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4821,7 +4821,7 @@
         <v>30</v>
       </c>
       <c r="F75" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -4863,12 +4863,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0227_03_3.13</t>
+          <t>0214_00_G.23</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0110_02_2.01</t>
+          <t>0001_01_1.267</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4939,7 +4939,7 @@
         <v>25</v>
       </c>
       <c r="F77" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -4981,12 +4981,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0335_03_3.1</t>
+          <t>0110_02_2.01</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0113_03_3.3</t>
+          <t>0227_02_2.30</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0113_01M_01M.467</t>
+          <t>0113_00_G.13</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5116,7 +5116,7 @@
         <v>25</v>
       </c>
       <c r="F80" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0209_02_2.37</t>
+          <t>0300_00_NG.02</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5234,7 +5234,7 @@
         <v>30</v>
       </c>
       <c r="F82" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0335_03_3.1</t>
+          <t>0113_01M_01M.467</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5335,7 +5335,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0201_02_2.11</t>
+          <t>0251_01_1.01</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5394,12 +5394,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0227_00_G.04</t>
+          <t>0310_00_G.Z02</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Tuesday 11:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0110_02_2.01</t>
+          <t>0335_03_3.1</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0335_05_5.3</t>
+          <t>0226_01_1.02</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Friday 15:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5571,12 +5571,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0227_01_1.06</t>
+          <t>0008_03_3.454</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5630,12 +5630,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0335_03_3.1</t>
+          <t>0228_09_9.18</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5748,12 +5748,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0001_01_1.275</t>
+          <t>0335_04_4.2</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5765,7 +5765,7 @@
         <v>30</v>
       </c>
       <c r="F91" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -5807,12 +5807,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0201_00_G.05</t>
+          <t>0201_01_1.05</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0113_00_G.03</t>
+          <t>0335_05_5.3</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Monday 11:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5925,12 +5925,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0450_02_2.63</t>
+          <t>0112_04_4.11</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5942,7 +5942,7 @@
         <v>5</v>
       </c>
       <c r="F94" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -6043,12 +6043,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0201_02_2.11</t>
+          <t>0113_01_1.434</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6107,7 +6107,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Monday 11:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0251_01_1.02</t>
+          <t>0201_02_2.11</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6220,12 +6220,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0001_01_1.275</t>
+          <t>0335_05_5.2</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6237,7 +6237,7 @@
         <v>30</v>
       </c>
       <c r="F99" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0228_-1_LG.07</t>
+          <t>0008_03_3.454</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0335_05_5.1</t>
+          <t>0112_-1_B.06</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0001_00_G.158</t>
+          <t>0335_04_4.2</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6414,7 +6414,7 @@
         <v>30</v>
       </c>
       <c r="F102" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0228_09_9.18</t>
+          <t>0113_00_G.14</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -6473,7 +6473,7 @@
         <v>25</v>
       </c>
       <c r="F103" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -6515,12 +6515,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0201_01_1.01</t>
+          <t>0103_01_1.B10</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -6574,12 +6574,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0201_01_1.05</t>
+          <t>0201_07_7.01</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6633,12 +6633,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Monday 15:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6650,7 +6650,7 @@
         <v>120</v>
       </c>
       <c r="F106" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Tuesday 16:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Wednesday 15:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -6768,7 +6768,7 @@
         <v>120</v>
       </c>
       <c r="F108" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -6810,12 +6810,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0113_00_G.03</t>
+          <t>0226_01_1.02</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Thursday 11:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0227_00_G.01</t>
+          <t>0335_00_G.10</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -6886,7 +6886,7 @@
         <v>30</v>
       </c>
       <c r="F110" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -6928,12 +6928,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0103_03_3.D02</t>
+          <t>0214_00_G.02</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0228_04_4.18</t>
+          <t>0001_01_1.267</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -7004,7 +7004,7 @@
         <v>25</v>
       </c>
       <c r="F112" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -7046,12 +7046,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0001_01_1.275</t>
+          <t>0335_00_G.09</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -7063,7 +7063,7 @@
         <v>30</v>
       </c>
       <c r="F113" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -7105,12 +7105,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0450_01_1.63</t>
+          <t>0450_03_3.32</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -7122,7 +7122,7 @@
         <v>5</v>
       </c>
       <c r="F114" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -7164,12 +7164,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0113_01_1.416</t>
+          <t>0335_02_2.3</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -7223,12 +7223,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0008_00_G.251</t>
+          <t>0228_07_7.18</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -7282,12 +7282,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0251_01_1.02</t>
+          <t>0008_-1_B.157</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -7341,12 +7341,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0113_02M_02M.24</t>
+          <t>0210_00-GFSSR4</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -7405,7 +7405,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Thursday 16:00</t>
+          <t>Friday 10:00</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0335_03_3.4</t>
+          <t>0254_01_1.08</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -7518,12 +7518,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0450_04_4.35</t>
+          <t>0335_04_4.2</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -7535,7 +7535,7 @@
         <v>30</v>
       </c>
       <c r="F121" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -7577,12 +7577,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Friday 13:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -7594,7 +7594,7 @@
         <v>120</v>
       </c>
       <c r="F122" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -7636,12 +7636,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0113_01M_01M.467</t>
+          <t>0113_00_G.14</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -7653,7 +7653,7 @@
         <v>25</v>
       </c>
       <c r="F123" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -7695,12 +7695,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0001_00_G.158</t>
+          <t>0335_00_G.09</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -7712,7 +7712,7 @@
         <v>30</v>
       </c>
       <c r="F124" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -7759,7 +7759,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -7813,12 +7813,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -7830,7 +7830,7 @@
         <v>120</v>
       </c>
       <c r="F126" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -7931,12 +7931,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0113_01_1.42</t>
+          <t>0450_01_1.52</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -7948,7 +7948,7 @@
         <v>20</v>
       </c>
       <c r="F128" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -7990,12 +7990,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0103_01_1.B04</t>
+          <t>0003_00_G.01</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0209_-1_B.Z28</t>
+          <t>0311_02_2.02</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -8108,12 +8108,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0335_01_1.1</t>
+          <t>0112_-1_B.06</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -8167,12 +8167,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0113_01M_01M.467</t>
+          <t>0001_01_1.267</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -8184,7 +8184,7 @@
         <v>25</v>
       </c>
       <c r="F132" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -8226,12 +8226,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0001_00_G.158</t>
+          <t>0335_00_G.09</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -8243,7 +8243,7 @@
         <v>30</v>
       </c>
       <c r="F133" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -8285,12 +8285,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0335_03_3.1</t>
+          <t>0001_01_1.267</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -8302,7 +8302,7 @@
         <v>25</v>
       </c>
       <c r="F134" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -8344,12 +8344,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0227_00_G.01</t>
+          <t>0335_00_G.09</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -8361,7 +8361,7 @@
         <v>30</v>
       </c>
       <c r="F135" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -8403,12 +8403,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0103_01_1.B04</t>
+          <t>0113_00_G.204</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Friday 10:00</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -8462,12 +8462,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0335_01_1.3</t>
+          <t>0335_00_G.10</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -8479,7 +8479,7 @@
         <v>30</v>
       </c>
       <c r="F137" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0219_00_G.02</t>
+          <t>0003_01_1.03</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0110_02_2.01</t>
+          <t>0113_00_G.13</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -8597,7 +8597,7 @@
         <v>25</v>
       </c>
       <c r="F139" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -8639,12 +8639,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Monday 11:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -8656,7 +8656,7 @@
         <v>120</v>
       </c>
       <c r="F140" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>0228_11_11.18</t>
+          <t>0228_07_7.18</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -8762,7 +8762,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Friday 16:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -8816,12 +8816,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0113_01M_01M.467</t>
+          <t>0001_01_1.267</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -8833,7 +8833,7 @@
         <v>25</v>
       </c>
       <c r="F143" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -8875,12 +8875,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0335_01_1.3</t>
+          <t>0112_-1_B.01</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -8892,7 +8892,7 @@
         <v>30</v>
       </c>
       <c r="F144" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -8934,12 +8934,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0112_-1_B.06</t>
+          <t>0251_01_1.02</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -8951,7 +8951,7 @@
         <v>25</v>
       </c>
       <c r="F145" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -8993,12 +8993,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0335_04_4.1</t>
+          <t>0335_05_5.2</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -9010,7 +9010,7 @@
         <v>30</v>
       </c>
       <c r="F146" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -9052,12 +9052,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>0450_04_4.35</t>
+          <t>0335_00_G.10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -9069,7 +9069,7 @@
         <v>30</v>
       </c>
       <c r="F147" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -9111,12 +9111,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>0201_02_2.14</t>
+          <t>0201_05_5.05</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -9128,7 +9128,7 @@
         <v>50</v>
       </c>
       <c r="F148" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -9170,12 +9170,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>0001_01_1.275</t>
+          <t>0335_01_1.9</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -9187,7 +9187,7 @@
         <v>30</v>
       </c>
       <c r="F149" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -9229,12 +9229,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>0008_01_1.302</t>
+          <t>0001_01_1.267</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -9246,7 +9246,7 @@
         <v>25</v>
       </c>
       <c r="F150" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -9288,12 +9288,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>0001_00_G.158</t>
+          <t>0201_04_4.12</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -9305,7 +9305,7 @@
         <v>30</v>
       </c>
       <c r="F151" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -9347,12 +9347,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>0210_00_GFS2</t>
+          <t>0103_01_1.B04</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Friday 10:00</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -9406,7 +9406,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>0228_09_9.18</t>
+          <t>0283_01_1.17</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9423,7 +9423,7 @@
         <v>25</v>
       </c>
       <c r="F153" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -9465,12 +9465,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>0113_00_G.203</t>
+          <t>0210_00_GFS2</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>0335_01_1.3</t>
+          <t>0335_00_G.09</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -9541,7 +9541,7 @@
         <v>30</v>
       </c>
       <c r="F155" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>0335_04_4.1</t>
+          <t>0335_00_G.10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -9659,7 +9659,7 @@
         <v>30</v>
       </c>
       <c r="F157" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -9701,12 +9701,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>0001_01_1.275</t>
+          <t>0335_01_1.9</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -9718,7 +9718,7 @@
         <v>30</v>
       </c>
       <c r="F158" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
@@ -9760,12 +9760,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>0335_05_5.1</t>
+          <t>0283_01_1.17</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -9777,7 +9777,7 @@
         <v>25</v>
       </c>
       <c r="F159" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
@@ -9819,12 +9819,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>0113_00_G.204</t>
+          <t>0201_02_2.07</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Friday 10:00</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>0008_00_G.267</t>
+          <t>0335_00_G.10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -9895,7 +9895,7 @@
         <v>30</v>
       </c>
       <c r="F161" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -9937,12 +9937,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>0335_02_2.1</t>
+          <t>0003_03_3.01</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -9954,7 +9954,7 @@
         <v>25</v>
       </c>
       <c r="F162" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
@@ -9996,12 +9996,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>0001_01_1.275</t>
+          <t>0335_05_5.2</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -10013,7 +10013,7 @@
         <v>30</v>
       </c>
       <c r="F163" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -10055,12 +10055,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>0311_02_2.02</t>
+          <t>0227_01_1.06</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -10114,12 +10114,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>0201_05_5.01</t>
+          <t>0201_02_2.04</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Friday 10:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -10131,7 +10131,7 @@
         <v>20</v>
       </c>
       <c r="F165" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
@@ -10173,12 +10173,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>0335_01_1.3</t>
+          <t>0335_02_2.14</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -10190,7 +10190,7 @@
         <v>30</v>
       </c>
       <c r="F166" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -10232,12 +10232,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>0335_03_3.1</t>
+          <t>0228_04_4.18</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>0335_01_1.3</t>
+          <t>0228_-1_LG.06</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Friday 10:00</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -10308,7 +10308,7 @@
         <v>30</v>
       </c>
       <c r="F168" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
@@ -10350,12 +10350,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>0311_02_2.02</t>
+          <t>0422_J_J.05</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -10409,12 +10409,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>0003_00_G.01</t>
+          <t>0201_01_1.05</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Friday 10:00</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -10468,12 +10468,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>0311_02_2.02</t>
+          <t>0228_-1_LG.07</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -10527,12 +10527,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>0001_01_1.275</t>
+          <t>0450_03_3.35</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -10544,7 +10544,7 @@
         <v>30</v>
       </c>
       <c r="F172" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
@@ -10586,12 +10586,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Wednesday 16:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -10603,7 +10603,7 @@
         <v>120</v>
       </c>
       <c r="F173" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
@@ -10650,7 +10650,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -10704,12 +10704,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>0335_02_2.1</t>
+          <t>0228_09_9.18</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>0209_02_2.37</t>
+          <t>0335_00_G.09</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -10780,7 +10780,7 @@
         <v>30</v>
       </c>
       <c r="F176" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
@@ -10822,12 +10822,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>0450_02_2.63</t>
+          <t>0113_01_1.26</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -10839,7 +10839,7 @@
         <v>2</v>
       </c>
       <c r="F177" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
@@ -10881,12 +10881,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>0335_05_5.3</t>
+          <t>0201_05_5.05</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Friday 13:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -10898,7 +10898,7 @@
         <v>50</v>
       </c>
       <c r="F178" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
@@ -10999,12 +10999,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>0001_00_G.158</t>
+          <t>0335_00_G.09</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -11016,7 +11016,7 @@
         <v>30</v>
       </c>
       <c r="F180" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
@@ -11058,12 +11058,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>0008_01_1.302</t>
+          <t>0335_01_1.1</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Friday 15:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -11117,12 +11117,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>0227_01_1.06</t>
+          <t>0422_J_J.03</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -11176,12 +11176,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Monday 16:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -11193,7 +11193,7 @@
         <v>120</v>
       </c>
       <c r="F183" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
@@ -11235,12 +11235,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>0103_01_1.B19</t>
+          <t>0001_01_1.276</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -11252,7 +11252,7 @@
         <v>20</v>
       </c>
       <c r="F184" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
@@ -11294,12 +11294,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>0001_02_2.343</t>
+          <t>0228_11_11.01</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -11353,12 +11353,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>0209_-1_B.Z28</t>
+          <t>0228_-1_LG.07</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -11412,12 +11412,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>0227_00_G.01</t>
+          <t>0112_-1_B.01</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Friday 10:00</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -11429,7 +11429,7 @@
         <v>30</v>
       </c>
       <c r="F187" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
@@ -11471,12 +11471,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Tuesday 11:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -11488,7 +11488,7 @@
         <v>120</v>
       </c>
       <c r="F188" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
@@ -11530,12 +11530,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>0113_00_G.203</t>
+          <t>0201_01_1.01</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -11591,12 +11591,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>0003_00_G.03</t>
+          <t>0335_00_G.12</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -11608,7 +11608,7 @@
         <v>17</v>
       </c>
       <c r="F190" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
@@ -11652,12 +11652,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>0201_02_2.06</t>
+          <t>0335_00_G.12</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -11669,7 +11669,7 @@
         <v>17</v>
       </c>
       <c r="F191" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
@@ -11713,12 +11713,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR4</t>
+          <t>0113_00M_00M.03</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -11774,12 +11774,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>0228_09_9.18</t>
+          <t>0335_01_1.1</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -11835,12 +11835,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>0001_01_1.274</t>
+          <t>0450_01_1.52</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -11852,7 +11852,7 @@
         <v>21</v>
       </c>
       <c r="F194" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
@@ -11896,12 +11896,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>0214_01_1.10</t>
+          <t>0335_00_G.12</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Friday 10:00</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -11913,7 +11913,7 @@
         <v>17</v>
       </c>
       <c r="F195" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
@@ -11957,12 +11957,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>0201_02_2.11</t>
+          <t>0251_01_1.01</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -12018,12 +12018,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>0113_00_G.200</t>
+          <t>0219_00_G.01</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -12079,12 +12079,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>0113_00_G.199</t>
+          <t>0283_01_1.01</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -12096,7 +12096,7 @@
         <v>5</v>
       </c>
       <c r="F198" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
@@ -12140,12 +12140,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>0335_02_2.1</t>
+          <t>0113_00_G.13</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Friday 13:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -12157,7 +12157,7 @@
         <v>25</v>
       </c>
       <c r="F199" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
@@ -12201,12 +12201,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>0001_00_G.158</t>
+          <t>0335_00_G.09</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -12218,7 +12218,7 @@
         <v>30</v>
       </c>
       <c r="F200" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
@@ -12262,12 +12262,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>0112_-1_B.06</t>
+          <t>0335_05_5.1</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -12323,12 +12323,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>0450_03_3.63</t>
+          <t>0254_01_1.12</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -12340,7 +12340,7 @@
         <v>6</v>
       </c>
       <c r="F202" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
@@ -12384,12 +12384,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>0112_-1_B.06</t>
+          <t>0008_01_1.302</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>0251_01_1.02</t>
+          <t>0003_03_3.01</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -12511,7 +12511,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -12572,7 +12572,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -12628,12 +12628,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>0228_03_3.01</t>
+          <t>0219_00_G.02</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -12689,12 +12689,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>0001_02_2.349</t>
+          <t>0113_00_G.200</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>0227_00_G.01</t>
+          <t>0335_00_G.10</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -12767,7 +12767,7 @@
         <v>30</v>
       </c>
       <c r="F209" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
@@ -12811,12 +12811,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>0254_01_1.01</t>
+          <t>0113_03_3.3</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -12828,7 +12828,7 @@
         <v>6</v>
       </c>
       <c r="F210" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
@@ -12872,12 +12872,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>0254_01_1.09</t>
+          <t>0113_01M_01M.20</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -12889,7 +12889,7 @@
         <v>4</v>
       </c>
       <c r="F211" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
@@ -12933,12 +12933,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>0219_00_G.02</t>
+          <t>0201_02_2.05</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -12994,7 +12994,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>0113_01_1.434</t>
+          <t>0008_-1_B.157</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>0201_02_2.04</t>
+          <t>0008_00_G.251</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -13116,12 +13116,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>0335_03_3.1</t>
+          <t>0283_01_1.17</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -13133,7 +13133,7 @@
         <v>25</v>
       </c>
       <c r="F215" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
@@ -13177,12 +13177,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>0201_05_5.01</t>
+          <t>0201_01_1.01</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -13238,12 +13238,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>0113_01M_01M.474</t>
+          <t>0112_02_2.11</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -13255,7 +13255,7 @@
         <v>10</v>
       </c>
       <c r="F217" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
@@ -13299,12 +13299,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>0113_01M_01M.467</t>
+          <t>0113_00_G.14</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -13316,7 +13316,7 @@
         <v>25</v>
       </c>
       <c r="F218" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
@@ -13360,12 +13360,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>0209_01_1.21</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -13377,7 +13377,7 @@
         <v>125</v>
       </c>
       <c r="F219" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
@@ -13421,12 +13421,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>0228_09_9.18</t>
+          <t>0335_05_5.1</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -13482,12 +13482,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>0110_02_2.01</t>
+          <t>0228_09_9.18</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>0335_05_5.1</t>
+          <t>0008_-1_B.157</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -13560,7 +13560,7 @@
         <v>25</v>
       </c>
       <c r="F222" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
@@ -13604,12 +13604,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>0209_01_1.21</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -13621,7 +13621,7 @@
         <v>125</v>
       </c>
       <c r="F223" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
@@ -13670,7 +13670,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -13731,7 +13731,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -13792,7 +13792,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -13848,12 +13848,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>0008_01_1.302</t>
+          <t>0283_01_1.17</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -13865,7 +13865,7 @@
         <v>25</v>
       </c>
       <c r="F227" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
@@ -13909,12 +13909,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>0110_02_2.01</t>
+          <t>0113_00_G.13</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -13926,7 +13926,7 @@
         <v>25</v>
       </c>
       <c r="F228" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -14031,12 +14031,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>0335_05_5.1</t>
+          <t>0335_03_3.1</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -14092,12 +14092,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>0001_00_G.158</t>
+          <t>0335_00_G.10</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -14109,7 +14109,7 @@
         <v>30</v>
       </c>
       <c r="F231" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
@@ -14153,12 +14153,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>0450_04_4.35</t>
+          <t>0335_01_1.9</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -14170,7 +14170,7 @@
         <v>30</v>
       </c>
       <c r="F232" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Friday 10:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -14275,12 +14275,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>0335_01_1.3</t>
+          <t>0335_01_1.9</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -14292,7 +14292,7 @@
         <v>30</v>
       </c>
       <c r="F234" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
@@ -14336,12 +14336,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>0335_03_3.1</t>
+          <t>0335_02_2.1</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -14397,12 +14397,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>0226_04_4.04</t>
+          <t>0201_05_5.05</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -14414,7 +14414,7 @@
         <v>50</v>
       </c>
       <c r="F236" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>0227_03_3.30</t>
+          <t>0003_01_1.05</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -14475,7 +14475,7 @@
         <v>9</v>
       </c>
       <c r="F237" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
@@ -14519,12 +14519,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>0112_-1_B.06</t>
+          <t>0283_01_1.17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -14536,7 +14536,7 @@
         <v>25</v>
       </c>
       <c r="F238" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G238" t="inlineStr">
         <is>
@@ -14580,12 +14580,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>0335_03_3.1</t>
+          <t>0110_02_2.01</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -14641,12 +14641,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>0113_00M_00M.03</t>
+          <t>0112_04_4.11</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -14658,7 +14658,7 @@
         <v>10</v>
       </c>
       <c r="F240" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
@@ -14702,12 +14702,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>0113_01M_01M.467</t>
+          <t>0251_01_1.02</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -14719,7 +14719,7 @@
         <v>25</v>
       </c>
       <c r="F241" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
@@ -14763,12 +14763,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>0335_05_5.1</t>
+          <t>0113_01M_01M.467</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -14824,12 +14824,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>0008_-1_B.154</t>
+          <t>0227_02_2.14</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Thursday 16:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -14885,12 +14885,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>0228_09_9.18</t>
+          <t>0112_-1_B.06</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -14946,12 +14946,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>0001_01_1.274</t>
+          <t>0311_02_2.01</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -15007,12 +15007,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>0335_02_2.3</t>
+          <t>0112_-1_B.02</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -15068,12 +15068,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>0008_00_G.267</t>
+          <t>0335_00_G.09</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -15085,7 +15085,7 @@
         <v>30</v>
       </c>
       <c r="F247" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G247" t="inlineStr">
         <is>
@@ -15129,12 +15129,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>0001_01_1.275</t>
+          <t>0335_00_G.10</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -15146,7 +15146,7 @@
         <v>30</v>
       </c>
       <c r="F248" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G248" t="inlineStr">
         <is>
@@ -15190,12 +15190,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>0300_00_NG.04</t>
+          <t>0103_01_1.B15</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -15251,12 +15251,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>0103_01_1.B04</t>
+          <t>0201_01_1.05</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -15312,12 +15312,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>0110_02_2.01</t>
+          <t>0335_02_2.1</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -15434,12 +15434,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>0113_01M_01M.467</t>
+          <t>0228_04_4.18</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -15495,12 +15495,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>0001_02_2.347</t>
+          <t>0001_02_2.351</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -15561,7 +15561,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -15617,12 +15617,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>0228_09_9.18</t>
+          <t>0113_00_G.14</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -15634,7 +15634,7 @@
         <v>25</v>
       </c>
       <c r="F256" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G256" t="inlineStr">
         <is>
@@ -15678,12 +15678,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>0311_02_2.02</t>
+          <t>0422_J_J.03</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -15744,7 +15744,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -15800,12 +15800,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>0008_01_1.302</t>
+          <t>0228_04_4.18</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -15861,12 +15861,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>0113_01M_01M.467</t>
+          <t>0113_00_G.14</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -15878,7 +15878,7 @@
         <v>25</v>
       </c>
       <c r="F260" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G260" t="inlineStr">
         <is>
@@ -15922,12 +15922,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>0001_00_G.158</t>
+          <t>0335_00_G.10</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -15939,7 +15939,7 @@
         <v>30</v>
       </c>
       <c r="F261" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G261" t="inlineStr">
         <is>
@@ -15983,12 +15983,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>0335_01_1.1</t>
+          <t>0251_01_1.01</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -16000,7 +16000,7 @@
         <v>25</v>
       </c>
       <c r="F262" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G262" t="inlineStr">
         <is>
@@ -16044,12 +16044,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>0103_01_1.B10</t>
+          <t>0210_00_GFS2</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -16105,12 +16105,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>0335_02_2.18</t>
+          <t>0001_02_2.343</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -16171,7 +16171,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -16227,12 +16227,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>0110_02_2.01</t>
+          <t>0335_02_2.1</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -16288,12 +16288,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>0335_03_3.1</t>
+          <t>0112_-1_B.06</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Wednesday 14:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -16349,12 +16349,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>0201_02_2.07</t>
+          <t>0201_01_1.05</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -16415,7 +16415,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Tuesday 16:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -16471,12 +16471,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>0450_01_1.40</t>
+          <t>0113_00_G.03</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -16488,7 +16488,7 @@
         <v>50</v>
       </c>
       <c r="F270" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G270" t="inlineStr">
         <is>
@@ -16532,12 +16532,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>0001_01_1.273</t>
+          <t>0001_01_1.274</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>0450_04_4.35</t>
+          <t>0335_04_4.2</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -16610,7 +16610,7 @@
         <v>30</v>
       </c>
       <c r="F272" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -16654,12 +16654,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>0214_01_1.01</t>
+          <t>0201_01_1.01</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -16715,12 +16715,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>0335_04_4.1</t>
+          <t>0335_00_G.10</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -16732,7 +16732,7 @@
         <v>30</v>
       </c>
       <c r="F274" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -16776,12 +16776,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>0201_01_1.02</t>
+          <t>0228_-1_LG.09</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -16837,12 +16837,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>0228_09_9.18</t>
+          <t>0335_03_3.1</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -16898,12 +16898,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>0008_03_3.454</t>
+          <t>0228_-1_LG.07</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -16959,12 +16959,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>0209_01_1.21</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -16976,7 +16976,7 @@
         <v>125</v>
       </c>
       <c r="F278" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -17020,7 +17020,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>0335_01_1.1</t>
+          <t>0113_01M_01M.467</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -17086,7 +17086,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Thursday 16:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -17142,12 +17142,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>0228_09_9.18</t>
+          <t>0335_02_2.1</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -17203,12 +17203,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>0228_09_9.01</t>
+          <t>0300_00_NG.04</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -17264,12 +17264,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>0113_01_1.9</t>
+          <t>0112_-1_B.02</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -17325,12 +17325,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>0335_02_2.1</t>
+          <t>0335_01_1.1</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Wednesday 15:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -17386,12 +17386,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>0335_01_1.1</t>
+          <t>0201_02_2.11</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -17403,7 +17403,7 @@
         <v>25</v>
       </c>
       <c r="F285" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G285" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>0335_01_1.4</t>
+          <t>0335_02_2.18</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>0335_05_5.1</t>
+          <t>0113_00_G.14</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -17525,7 +17525,7 @@
         <v>25</v>
       </c>
       <c r="F287" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G287" t="inlineStr">
         <is>
@@ -17574,7 +17574,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -17630,12 +17630,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>0450_04_4.35</t>
+          <t>0335_05_5.2</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -17647,7 +17647,7 @@
         <v>30</v>
       </c>
       <c r="F289" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G289" t="inlineStr">
         <is>
@@ -17696,7 +17696,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -17752,12 +17752,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>0113_01_1.434</t>
+          <t>0251_01_1.01</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -17813,12 +17813,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>0003_01_1.02</t>
+          <t>0228_06_6.11</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -17874,12 +17874,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>0103_01_1.B10</t>
+          <t>0214_01_1.01</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -17935,12 +17935,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>0201_07_7.01</t>
+          <t>0210_00_GFS2</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -17996,12 +17996,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>0450_01_1.63</t>
+          <t>0210_00-GFSSR5</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -18013,7 +18013,7 @@
         <v>6</v>
       </c>
       <c r="F295" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G295" t="inlineStr">
         <is>
@@ -18057,12 +18057,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>0311_04_4.08</t>
+          <t>0228_01_1.01</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -18118,12 +18118,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>0112_-1_B.06</t>
+          <t>0113_00_G.14</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -18135,7 +18135,7 @@
         <v>25</v>
       </c>
       <c r="F297" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G297" t="inlineStr">
         <is>
@@ -18179,12 +18179,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>0201_00_G.05</t>
+          <t>0210_00_GFS2</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -18240,12 +18240,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>0113_01M_01M.467</t>
+          <t>0228_04_4.18</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -18301,12 +18301,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>0113_00_G.204</t>
+          <t>0201_01_1.05</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -18362,12 +18362,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>0219_00_G.01</t>
+          <t>0335_03_3.4</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Monday 16:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -18484,12 +18484,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>0335_01_1.1</t>
+          <t>0113_00_G.13</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -18501,7 +18501,7 @@
         <v>25</v>
       </c>
       <c r="F303" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G303" t="inlineStr">
         <is>
@@ -18545,12 +18545,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>0335_03_3.1</t>
+          <t>0113_00_G.13</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -18562,7 +18562,7 @@
         <v>25</v>
       </c>
       <c r="F304" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G304" t="inlineStr">
         <is>
@@ -18606,12 +18606,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>0113_01_1.416</t>
+          <t>0335_03_3.3</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -18667,12 +18667,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>0113_00_G.11</t>
+          <t>0113_00_G.10</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Friday 12:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -18728,12 +18728,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>0001_02_2.343</t>
+          <t>0254_01_1.03</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -18789,12 +18789,12 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>0335_05_5.1</t>
+          <t>0228_09_9.18</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -18850,12 +18850,12 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>0335_04_4.1</t>
+          <t>0335_04_4.2</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -18867,7 +18867,7 @@
         <v>30</v>
       </c>
       <c r="F309" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G309" t="inlineStr">
         <is>
@@ -18911,12 +18911,12 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>0113_00_G.12</t>
+          <t>0227_02_2.14</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Tuesday 11:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -18972,12 +18972,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>0113_01_1.42</t>
+          <t>0201_00_G.05</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -19033,12 +19033,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>0110_02_2.01</t>
+          <t>0008_01_1.302</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -19094,12 +19094,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>0335_01_1.1</t>
+          <t>0283_01_1.17</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -19111,7 +19111,7 @@
         <v>25</v>
       </c>
       <c r="F313" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G313" t="inlineStr">
         <is>
@@ -19155,12 +19155,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>0335_05_5.1</t>
+          <t>0251_01_1.02</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -19172,7 +19172,7 @@
         <v>25</v>
       </c>
       <c r="F314" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G314" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -19277,12 +19277,12 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>0001_01_1.265</t>
+          <t>0311_02_2.01</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -19338,12 +19338,12 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>0209_02_2.37</t>
+          <t>0335_00_G.10</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -19355,7 +19355,7 @@
         <v>30</v>
       </c>
       <c r="F317" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G317" t="inlineStr">
         <is>
@@ -19399,12 +19399,12 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>0103_01_1.B04</t>
+          <t>0201_02_2.07</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -19460,12 +19460,12 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>0335_05_5.1</t>
+          <t>0003_03_3.01</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -19477,7 +19477,7 @@
         <v>25</v>
       </c>
       <c r="F319" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G319" t="inlineStr">
         <is>
@@ -19521,12 +19521,12 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>0335_05_5.1</t>
+          <t>0113_00_G.13</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -19538,7 +19538,7 @@
         <v>25</v>
       </c>
       <c r="F320" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G320" t="inlineStr">
         <is>
@@ -19582,12 +19582,12 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>0210_00_GFS2</t>
+          <t>0113_00_G.204</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -19643,12 +19643,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>0201_07_7.01</t>
+          <t>0214_01_1.01</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Friday 10:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -19704,12 +19704,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>0201_05_5.01</t>
+          <t>0103_01_1.B10</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -19765,12 +19765,12 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>0450_04_4.35</t>
+          <t>0335_05_5.2</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -19782,7 +19782,7 @@
         <v>30</v>
       </c>
       <c r="F324" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G324" t="inlineStr">
         <is>
@@ -19826,12 +19826,12 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>0113_02_2.36</t>
+          <t>0201_02_2.04</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -19892,7 +19892,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -19953,7 +19953,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -20009,12 +20009,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>0003_00_G.01</t>
+          <t>0201_07_7.01</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -20070,12 +20070,12 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>0112_-1_B.06</t>
+          <t>0283_01_1.17</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -20087,7 +20087,7 @@
         <v>25</v>
       </c>
       <c r="F329" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G329" t="inlineStr">
         <is>
@@ -20136,7 +20136,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -20192,12 +20192,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>0001_01_1.275</t>
+          <t>0335_00_G.09</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -20209,7 +20209,7 @@
         <v>30</v>
       </c>
       <c r="F331" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G331" t="inlineStr">
         <is>
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>0228_09_9.18</t>
+          <t>0335_03_3.1</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -20380,7 +20380,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -20441,7 +20441,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -20502,7 +20502,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Thursday 15:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -20563,7 +20563,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -20619,12 +20619,12 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>0001_01_1.275</t>
+          <t>0228_-1_LG.06</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -20636,7 +20636,7 @@
         <v>30</v>
       </c>
       <c r="F338" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G338" t="inlineStr">
         <is>
@@ -20680,12 +20680,12 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>0228_-1_LG.07</t>
+          <t>0422_J_J.03</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -20741,12 +20741,12 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>0008_01_1.302</t>
+          <t>0113_00_G.13</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -20758,7 +20758,7 @@
         <v>25</v>
       </c>
       <c r="F340" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G340" t="inlineStr">
         <is>
@@ -20802,12 +20802,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>0335_02_2.1</t>
+          <t>0008_01_1.302</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -20868,7 +20868,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Wednesday 16:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -20924,12 +20924,12 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>0228_04_4.18</t>
+          <t>0251_01_1.02</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -20941,7 +20941,7 @@
         <v>25</v>
       </c>
       <c r="F343" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G343" t="inlineStr">
         <is>
@@ -20985,12 +20985,12 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>0008_01_1.302</t>
+          <t>0283_01_1.17</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -21002,7 +21002,7 @@
         <v>25</v>
       </c>
       <c r="F344" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G344" t="inlineStr">
         <is>
@@ -21051,7 +21051,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -21107,12 +21107,12 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>0201_01_1.02</t>
+          <t>0228_-1_LG.09</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Monday 13:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -21168,12 +21168,12 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>0110_02_2.01</t>
+          <t>0112_-1_B.06</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -21234,7 +21234,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -21290,12 +21290,12 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>0227_00_G.01</t>
+          <t>0335_05_5.2</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -21307,7 +21307,7 @@
         <v>30</v>
       </c>
       <c r="F349" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G349" t="inlineStr">
         <is>
@@ -21351,12 +21351,12 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>0008_01_1.302</t>
+          <t>0113_01M_01M.467</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -21412,12 +21412,12 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>0450_01_1.63</t>
+          <t>0227_02_2.13</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -21429,7 +21429,7 @@
         <v>6</v>
       </c>
       <c r="F351" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G351" t="inlineStr">
         <is>
@@ -21473,12 +21473,12 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>0003_03_3.01</t>
+          <t>0113_01_1.434</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -21539,7 +21539,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -21595,12 +21595,12 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>0110_02_2.01</t>
+          <t>0335_05_5.1</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -21656,12 +21656,12 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>0209_02_2.37</t>
+          <t>0335_05_5.2</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -21673,7 +21673,7 @@
         <v>30</v>
       </c>
       <c r="F355" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G355" t="inlineStr">
         <is>
@@ -21717,12 +21717,12 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>0008_02_2.418</t>
+          <t>0214_00_G.22</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -21778,12 +21778,12 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>0228_-1_LG.10</t>
+          <t>0313_00_G.10</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -21844,7 +21844,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Thursday 15:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -21900,12 +21900,12 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>0335_05_5.1</t>
+          <t>0228_09_9.18</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -21961,12 +21961,12 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>0209_01_1.21</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -21978,7 +21978,7 @@
         <v>125</v>
       </c>
       <c r="F360" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G360" t="inlineStr">
         <is>
@@ -22027,7 +22027,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Monday 11:00</t>
+          <t>Friday 10:00</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -22083,12 +22083,12 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>0227_03_3.54</t>
+          <t>0201_02_2.06</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -22144,12 +22144,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>0003_00_G.01</t>
+          <t>0201_01_1.05</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -22205,12 +22205,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>0228_04_4.18</t>
+          <t>0113_01_1.434</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -22222,7 +22222,7 @@
         <v>25</v>
       </c>
       <c r="F364" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G364" t="inlineStr">
         <is>
@@ -22266,12 +22266,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>0201_05_5.01</t>
+          <t>0103_01_1.B04</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -22327,12 +22327,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>0335_05_5.1</t>
+          <t>0283_01_1.17</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -22344,7 +22344,7 @@
         <v>25</v>
       </c>
       <c r="F366" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G366" t="inlineStr">
         <is>
@@ -22388,12 +22388,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>0113_00_G.203</t>
+          <t>0103_01_1.B19</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -22449,12 +22449,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>0113_01M_01M.467</t>
+          <t>0008_01_1.302</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -22510,12 +22510,12 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>0335_05_5.1</t>
+          <t>0201_02_2.11</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -22527,7 +22527,7 @@
         <v>25</v>
       </c>
       <c r="F369" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G369" t="inlineStr">
         <is>
@@ -22571,12 +22571,12 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>0113_01M_01M.474</t>
+          <t>0113_03_3.3</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -22632,12 +22632,12 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>0001_01_1.265</t>
+          <t>0001_01_1.273</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -22693,12 +22693,12 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>0201_02_2.07</t>
+          <t>0113_00_G.203</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -22754,12 +22754,12 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>0335_03_3.3</t>
+          <t>0335_03_3.2</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -22820,7 +22820,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -22876,12 +22876,12 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>0113_01M_01M.467</t>
+          <t>0110_02_2.01</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -22937,12 +22937,12 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>0226_00_GF.Z16</t>
+          <t>0113_00_G.152</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -22998,12 +22998,12 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>0008_00_G.267</t>
+          <t>0335_00_G.09</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -23015,7 +23015,7 @@
         <v>30</v>
       </c>
       <c r="F377" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G377" t="inlineStr">
         <is>
@@ -23059,12 +23059,12 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>0335_02_2.1</t>
+          <t>0113_01M_01M.467</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -23120,12 +23120,12 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>0113_01_1.434</t>
+          <t>0251_01_1.02</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -23181,12 +23181,12 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>0214_01_1.01</t>
+          <t>0113_01_1.42</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -23242,12 +23242,12 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>0335_04_4.1</t>
+          <t>0335_00_G.09</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -23259,7 +23259,7 @@
         <v>30</v>
       </c>
       <c r="F381" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G381" t="inlineStr">
         <is>
@@ -23308,7 +23308,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -23364,12 +23364,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>0227_02_2.54</t>
+          <t>0228_11_11.06</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -23425,12 +23425,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>0311_02_2.02</t>
+          <t>0422_J_J.03</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -23486,12 +23486,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>0227_01_1.06</t>
+          <t>0228_-1_LG.07</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -23552,7 +23552,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Monday 15:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -23608,12 +23608,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>0201_01_1.05</t>
+          <t>0201_07_7.01</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -23730,12 +23730,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>0008_00_G.252</t>
+          <t>0254_01_1.04</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -23791,12 +23791,12 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>0228_04_4.18</t>
+          <t>0251_01_1.01</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -23808,7 +23808,7 @@
         <v>25</v>
       </c>
       <c r="F390" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G390" t="inlineStr">
         <is>
@@ -23857,7 +23857,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Wednesday 15:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -23913,12 +23913,12 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>0227_00_G.04</t>
+          <t>0310_00_G.Z02</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Wednesday 14:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -23974,12 +23974,12 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>0003_01_1.01</t>
+          <t>0003_01_1.02</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -23991,7 +23991,7 @@
         <v>23</v>
       </c>
       <c r="F393" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G393" t="inlineStr">
         <is>
@@ -24035,12 +24035,12 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>0227_00_G.01</t>
+          <t>0335_01_1.9</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -24052,7 +24052,7 @@
         <v>30</v>
       </c>
       <c r="F394" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G394" t="inlineStr">
         <is>
@@ -24096,7 +24096,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>0113_01M_01M.467</t>
+          <t>0008_-1_B.157</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -24113,7 +24113,7 @@
         <v>25</v>
       </c>
       <c r="F395" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G395" t="inlineStr">
         <is>
@@ -24157,12 +24157,12 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>0450_02_2.63</t>
+          <t>0283_01_1.01</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -24174,7 +24174,7 @@
         <v>8</v>
       </c>
       <c r="F396" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G396" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -24279,12 +24279,12 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>0112_-1_B.06</t>
+          <t>0201_02_2.11</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -24296,7 +24296,7 @@
         <v>25</v>
       </c>
       <c r="F398" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G398" t="inlineStr">
         <is>
@@ -24340,12 +24340,12 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>0201_01_1.02</t>
+          <t>0228_-1_LG.09</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
@@ -24406,7 +24406,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -24462,12 +24462,12 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>0113_01M_01M.474</t>
+          <t>0113_00M_00M.07</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
@@ -24523,12 +24523,12 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>0335_03_3.1</t>
+          <t>0335_05_5.1</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
@@ -24584,12 +24584,12 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>0335_03_3.1</t>
+          <t>0110_02_2.01</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -24645,12 +24645,12 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>0251_01_1.02</t>
+          <t>0201_02_2.11</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
@@ -24706,12 +24706,12 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>0209_01_1.21</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -24723,7 +24723,7 @@
         <v>125</v>
       </c>
       <c r="F405" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G405" t="inlineStr">
         <is>
@@ -24767,12 +24767,12 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>0001_01_1.275</t>
+          <t>0335_05_5.2</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -24784,7 +24784,7 @@
         <v>30</v>
       </c>
       <c r="F406" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G406" t="inlineStr">
         <is>
@@ -24828,12 +24828,12 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>0219_00_G.02</t>
+          <t>0228_11_11.18</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -24889,12 +24889,12 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>0311_02_2.02</t>
+          <t>0335_04_4.3</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -24950,12 +24950,12 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>0201_02_2.11</t>
+          <t>0251_01_1.02</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
@@ -25011,12 +25011,12 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>0335_03_3.1</t>
+          <t>0335_01_1.1</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -25072,12 +25072,12 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>0008_01_1.302</t>
+          <t>0001_01_1.267</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -25089,7 +25089,7 @@
         <v>25</v>
       </c>
       <c r="F411" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G411" t="inlineStr">
         <is>
@@ -25133,12 +25133,12 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>0229_01_1.B</t>
+          <t>0229_01_1.C</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -25194,12 +25194,12 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>0335_02_2.1</t>
+          <t>0110_02_2.01</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -25255,12 +25255,12 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>0335_02_2.1</t>
+          <t>0113_00_G.14</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -25272,7 +25272,7 @@
         <v>25</v>
       </c>
       <c r="F414" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G414" t="inlineStr">
         <is>
@@ -25316,7 +25316,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>0227_02_2.14</t>
+          <t>0113_00_G.10</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -25377,12 +25377,12 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>0001_00_G.158</t>
+          <t>0335_01_1.9</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -25394,7 +25394,7 @@
         <v>30</v>
       </c>
       <c r="F416" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G416" t="inlineStr">
         <is>
@@ -25438,12 +25438,12 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>0335_02_2.1</t>
+          <t>0335_01_1.1</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -25504,7 +25504,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Wednesday 16:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -25560,12 +25560,12 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>0335_01_1.3</t>
+          <t>0335_04_4.2</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
@@ -25577,7 +25577,7 @@
         <v>30</v>
       </c>
       <c r="F419" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G419" t="inlineStr">
         <is>
@@ -25621,12 +25621,12 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>0227_00_G.01</t>
+          <t>0335_04_4.2</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -25638,7 +25638,7 @@
         <v>30</v>
       </c>
       <c r="F420" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G420" t="inlineStr">
         <is>
@@ -25682,12 +25682,12 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>0335_05_5.1</t>
+          <t>0001_01_1.267</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Friday 16:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
@@ -25699,7 +25699,7 @@
         <v>25</v>
       </c>
       <c r="F421" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G421" t="inlineStr">
         <is>
@@ -25743,12 +25743,12 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>0113_00M_00M.07</t>
+          <t>0227_02_2.13</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
@@ -25804,12 +25804,12 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>0335_04_4.1</t>
+          <t>0335_04_4.2</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -25821,7 +25821,7 @@
         <v>30</v>
       </c>
       <c r="F423" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G423" t="inlineStr">
         <is>
@@ -25865,12 +25865,12 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>0003_00_G.01</t>
+          <t>0103_01_1.B10</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
@@ -25931,7 +25931,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -25987,12 +25987,12 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>0210_00_GFS2</t>
+          <t>0214_01_1.01</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -26048,12 +26048,12 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>0112_-1_B.06</t>
+          <t>0335_03_3.1</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -26114,7 +26114,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -26170,12 +26170,12 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>0229_01_1.C</t>
+          <t>0229_01_1.B</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
@@ -26236,7 +26236,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Wednesday 15:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -26292,12 +26292,12 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>0450_03_3.42</t>
+          <t>0113_02_2.26</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
@@ -26309,7 +26309,7 @@
         <v>5</v>
       </c>
       <c r="F431" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G431" t="inlineStr">
         <is>
@@ -26353,12 +26353,12 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>0113_01_1.42</t>
+          <t>0210_00_GFS2</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -26414,12 +26414,12 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>0110_02_2.01</t>
+          <t>0228_04_4.18</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -26475,12 +26475,12 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>0335_01_1.1</t>
+          <t>0335_02_2.1</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -26536,12 +26536,12 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>0227_02_2.39</t>
+          <t>0003_02_2.01</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -26597,12 +26597,12 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>0450_02_2.20</t>
+          <t>0201_05_5.05</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -26614,7 +26614,7 @@
         <v>50</v>
       </c>
       <c r="F436" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G436" t="inlineStr">
         <is>
@@ -26658,12 +26658,12 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>0103_01_1.B19</t>
+          <t>0214_01_1.01</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -26719,12 +26719,12 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>0335_02_2.1</t>
+          <t>0112_-1_B.06</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
@@ -26785,7 +26785,7 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
@@ -26841,12 +26841,12 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>0450_04_4.35</t>
+          <t>0335_00_G.10</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
@@ -26858,7 +26858,7 @@
         <v>30</v>
       </c>
       <c r="F440" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G440" t="inlineStr">
         <is>
@@ -26902,7 +26902,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>0335_01_1.1</t>
+          <t>0003_03_3.01</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -26919,7 +26919,7 @@
         <v>25</v>
       </c>
       <c r="F441" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G441" t="inlineStr">
         <is>
@@ -26963,12 +26963,12 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>0001_02_2.349</t>
+          <t>0300_00_NG.03</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
@@ -27024,12 +27024,12 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>0001_02_2.347</t>
+          <t>0228_09_9.01</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
@@ -27085,12 +27085,12 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>0251_01_1.01</t>
+          <t>0113_01_1.434</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
@@ -27146,12 +27146,12 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>0335_03_3.2</t>
+          <t>0227_01_1.02</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -27207,12 +27207,12 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>0113_01M_01M.467</t>
+          <t>0228_09_9.18</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
@@ -27268,12 +27268,12 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>0228_09_9.18</t>
+          <t>0113_00_G.14</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -27285,7 +27285,7 @@
         <v>25</v>
       </c>
       <c r="F447" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G447" t="inlineStr">
         <is>
@@ -27329,12 +27329,12 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>0201_01_1.02</t>
+          <t>0228_-1_LG.09</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
@@ -27451,12 +27451,12 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>0112_-1_B.06</t>
+          <t>0335_02_2.1</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
@@ -27512,12 +27512,12 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>0001_01_1.270</t>
+          <t>0103_01_1.B15</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
@@ -27573,12 +27573,12 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>0228_04_4.18</t>
+          <t>0113_00_G.13</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
@@ -27590,7 +27590,7 @@
         <v>25</v>
       </c>
       <c r="F452" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G452" t="inlineStr">
         <is>
@@ -27634,12 +27634,12 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>0335_02_2.18</t>
+          <t>0001_02_2.349</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
@@ -27695,12 +27695,12 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>0210_00_GFS2</t>
+          <t>0113_01_1.42</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Friday 10:00</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
@@ -27817,12 +27817,12 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>0008_00_G.267</t>
+          <t>0335_00_G.09</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
@@ -27834,7 +27834,7 @@
         <v>30</v>
       </c>
       <c r="F456" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G456" t="inlineStr">
         <is>
@@ -27878,12 +27878,12 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>0335_02_2.1</t>
+          <t>0113_00_G.13</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
@@ -27895,7 +27895,7 @@
         <v>25</v>
       </c>
       <c r="F457" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G457" t="inlineStr">
         <is>
@@ -27944,7 +27944,7 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
@@ -28000,12 +28000,12 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>0201_00_G.05</t>
+          <t>0214_01_1.01</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
@@ -28061,12 +28061,12 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>0001_01_1.276</t>
+          <t>0001_01_1.265</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>0112_-1_B.06</t>
+          <t>0113_01_1.434</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -28139,7 +28139,7 @@
         <v>25</v>
       </c>
       <c r="F461" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G461" t="inlineStr">
         <is>
@@ -28183,12 +28183,12 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>0008_00_G.252</t>
+          <t>0335_02_2.18</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
@@ -28249,7 +28249,7 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
@@ -28305,12 +28305,12 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>0335_01_1.1</t>
+          <t>0003_03_3.01</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
@@ -28322,7 +28322,7 @@
         <v>25</v>
       </c>
       <c r="F464" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G464" t="inlineStr">
         <is>
@@ -28366,7 +28366,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>0228_08_8.13</t>
+          <t>0227_02_2.29</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -28427,12 +28427,12 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>0003_00_G.01</t>
+          <t>0113_00_G.203</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Friday 10:00</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
@@ -28488,12 +28488,12 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>0335_01_1.3</t>
+          <t>0335_05_5.2</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
@@ -28505,7 +28505,7 @@
         <v>30</v>
       </c>
       <c r="F467" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G467" t="inlineStr">
         <is>
@@ -28549,12 +28549,12 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>0310_00_G.Z02</t>
+          <t>0227_00_G.04</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
@@ -28610,12 +28610,12 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>0001_01_1.273</t>
+          <t>0001_01_1.276</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
@@ -28671,12 +28671,12 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>0228_04_4.18</t>
+          <t>0283_01_1.17</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Wednesday 15:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
@@ -28688,7 +28688,7 @@
         <v>25</v>
       </c>
       <c r="F470" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G470" t="inlineStr">
         <is>
@@ -28732,12 +28732,12 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>0008_02_2.365</t>
+          <t>0254_01_1.04</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
@@ -28798,7 +28798,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
@@ -28854,12 +28854,12 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>0201_05_5.01</t>
+          <t>0103_01_1.B19</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
@@ -28915,12 +28915,12 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>0335_01_1.1</t>
+          <t>0113_00_G.14</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
@@ -28932,7 +28932,7 @@
         <v>25</v>
       </c>
       <c r="F474" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G474" t="inlineStr">
         <is>
@@ -28976,12 +28976,12 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>0001_01_1.274</t>
+          <t>0001_01_1.265</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
@@ -29042,7 +29042,7 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
@@ -29098,12 +29098,12 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>0103_01_1.B19</t>
+          <t>0201_01_1.05</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
@@ -29159,12 +29159,12 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>0228_04_4.18</t>
+          <t>0113_00_G.14</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
@@ -29176,7 +29176,7 @@
         <v>25</v>
       </c>
       <c r="F478" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G478" t="inlineStr">
         <is>
@@ -29220,12 +29220,12 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>0254_01_1.5A</t>
+          <t>0227_03_3.13</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
@@ -29237,7 +29237,7 @@
         <v>2</v>
       </c>
       <c r="F479" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G479" t="inlineStr">
         <is>
@@ -29281,12 +29281,12 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>0113_00_G.203</t>
+          <t>0201_02_2.07</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
@@ -29342,12 +29342,12 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>0450_04_4.35</t>
+          <t>0335_00_G.09</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
@@ -29359,7 +29359,7 @@
         <v>30</v>
       </c>
       <c r="F481" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G481" t="inlineStr">
         <is>
@@ -29403,12 +29403,12 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>0227_03_3.14</t>
+          <t>0228_08_8.13</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Tuesday 16:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
@@ -29464,12 +29464,12 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>0113_00_G.203</t>
+          <t>0201_07_7.01</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>0335_03_3.1</t>
+          <t>0113_01M_01M.467</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
@@ -29586,12 +29586,12 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>0254_01_1.08</t>
+          <t>0228_11_11.01</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
@@ -29647,12 +29647,12 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>0008_01_1.302</t>
+          <t>0003_03_3.01</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
@@ -29664,7 +29664,7 @@
         <v>25</v>
       </c>
       <c r="F486" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G486" t="inlineStr">
         <is>
@@ -29713,7 +29713,7 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
@@ -29769,12 +29769,12 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>0001_00_G.158</t>
+          <t>0335_00_G.10</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
@@ -29786,7 +29786,7 @@
         <v>30</v>
       </c>
       <c r="F488" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G488" t="inlineStr">
         <is>
@@ -29830,12 +29830,12 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>0112_-1_B.06</t>
+          <t>0335_03_3.1</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
@@ -29891,12 +29891,12 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>0254_01_1.5A</t>
+          <t>0227_02_2.30</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
@@ -29908,7 +29908,7 @@
         <v>6</v>
       </c>
       <c r="F490" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G490" t="inlineStr">
         <is>
@@ -29957,7 +29957,7 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
@@ -30013,12 +30013,12 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>0201_07_7.14</t>
+          <t>0008_02_2.418</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
@@ -30074,12 +30074,12 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>0209_02_2.37</t>
+          <t>0335_00_G.09</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
@@ -30091,7 +30091,7 @@
         <v>30</v>
       </c>
       <c r="F493" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G493" t="inlineStr">
         <is>
@@ -30135,12 +30135,12 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>0008_-1_B.153</t>
+          <t>0227_02_2.14</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Tuesday 11:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
@@ -30196,12 +30196,12 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>0008_00_G.267</t>
+          <t>0335_01_1.9</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
@@ -30213,7 +30213,7 @@
         <v>30</v>
       </c>
       <c r="F495" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G495" t="inlineStr">
         <is>
@@ -30257,12 +30257,12 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>0335_03_3.1</t>
+          <t>0001_01_1.267</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
@@ -30274,7 +30274,7 @@
         <v>25</v>
       </c>
       <c r="F496" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G496" t="inlineStr">
         <is>
@@ -30323,7 +30323,7 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
@@ -30379,12 +30379,12 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>0001_01_1.275</t>
+          <t>0335_00_G.10</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
@@ -30396,7 +30396,7 @@
         <v>30</v>
       </c>
       <c r="F498" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G498" t="inlineStr">
         <is>
@@ -30440,12 +30440,12 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>0112_-1_B.06</t>
+          <t>0001_01_1.267</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
@@ -30457,7 +30457,7 @@
         <v>25</v>
       </c>
       <c r="F499" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G499" t="inlineStr">
         <is>
@@ -30506,7 +30506,7 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
@@ -30567,7 +30567,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
@@ -30623,12 +30623,12 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>0001_01_1.275</t>
+          <t>0335_05_5.2</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
@@ -30640,7 +30640,7 @@
         <v>30</v>
       </c>
       <c r="F502" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G502" t="inlineStr">
         <is>
@@ -30684,12 +30684,12 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>0335_01_1.1</t>
+          <t>0113_00_G.14</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
@@ -30701,7 +30701,7 @@
         <v>25</v>
       </c>
       <c r="F503" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G503" t="inlineStr">
         <is>
@@ -30745,12 +30745,12 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>0201_07_7.02</t>
+          <t>0254_01_1.10</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
@@ -30806,12 +30806,12 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>0008_01_1.302</t>
+          <t>0110_02_2.01</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
@@ -30867,12 +30867,12 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>0209_-1_B.Z28</t>
+          <t>0228_-1_LG.07</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
@@ -30933,7 +30933,7 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
@@ -30989,12 +30989,12 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>0450_03_3.63</t>
+          <t>0227_02_2.30</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
@@ -31006,7 +31006,7 @@
         <v>6</v>
       </c>
       <c r="F508" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G508" t="inlineStr">
         <is>
@@ -31050,12 +31050,12 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>0228_04_4.18</t>
+          <t>0113_00_G.13</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
@@ -31067,7 +31067,7 @@
         <v>25</v>
       </c>
       <c r="F509" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G509" t="inlineStr">
         <is>
@@ -31111,12 +31111,12 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>0113_01_1.42</t>
+          <t>0003_00_G.01</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
@@ -31172,12 +31172,12 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>0209_02_2.37</t>
+          <t>0335_01_1.9</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
@@ -31189,7 +31189,7 @@
         <v>30</v>
       </c>
       <c r="F511" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G511" t="inlineStr">
         <is>
@@ -31233,12 +31233,12 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>0450_04_4.35</t>
+          <t>0335_05_5.2</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
@@ -31250,7 +31250,7 @@
         <v>30</v>
       </c>
       <c r="F512" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G512" t="inlineStr">
         <is>
@@ -31294,12 +31294,12 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>0228_04_4.18</t>
+          <t>0335_03_3.1</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
@@ -31360,7 +31360,7 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
@@ -31416,12 +31416,12 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>0201_02_2.07</t>
+          <t>0201_01_1.01</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Friday 10:00</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
@@ -31477,12 +31477,12 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>0201_05_5.07</t>
+          <t>0113_00_G.10</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Wednesday 14:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
@@ -31543,7 +31543,7 @@
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
@@ -31604,7 +31604,7 @@
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
@@ -31660,12 +31660,12 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>0201_01_1.08</t>
+          <t>0201_01_1.06</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Thursday 16:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
@@ -31677,7 +31677,7 @@
         <v>275</v>
       </c>
       <c r="F519" t="n">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="G519" t="inlineStr">
         <is>
@@ -31719,12 +31719,12 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>0113_00_G.204</t>
+          <t>0103_01_1.B04</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
@@ -31780,12 +31780,12 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>0001_01_1.274</t>
+          <t>0001_01_1.265</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
@@ -31846,7 +31846,7 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
@@ -31902,12 +31902,12 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>0335_05_5.1</t>
+          <t>0228_09_9.18</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
@@ -31963,12 +31963,12 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>0214_01_1.01</t>
+          <t>0201_02_2.07</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
